--- a/scenario/srw_hangzhou1/skus.xlsx
+++ b/scenario/srw_hangzhou1/skus.xlsx
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D121" t="n">
         <v>100</v>
@@ -3227,12 +3227,11 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D122" t="n">
         <v>100</v>
       </c>
-      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3246,7 +3245,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D123" t="n">
         <v>100</v>
@@ -3269,12 +3268,11 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D124" t="n">
         <v>100</v>
       </c>
-      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3288,12 +3286,11 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D125" t="n">
         <v>100</v>
       </c>
-      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3307,7 +3304,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D126" t="n">
         <v>100</v>
@@ -3330,7 +3327,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D127" t="n">
         <v>100</v>
@@ -3353,7 +3350,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D128" t="n">
         <v>100</v>
@@ -3376,7 +3373,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D129" t="n">
         <v>100</v>
@@ -3399,12 +3396,11 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D130" t="n">
         <v>100</v>
       </c>
-      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3418,7 +3414,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D131" t="n">
         <v>100</v>
@@ -3441,7 +3437,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D132" t="n">
         <v>100</v>
@@ -3464,7 +3460,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D133" t="n">
         <v>100</v>
@@ -3487,7 +3483,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D134" t="n">
         <v>24</v>
@@ -3510,7 +3506,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D135" t="n">
         <v>24</v>
@@ -3533,7 +3529,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D136" t="n">
         <v>24</v>
@@ -3556,7 +3552,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D137" t="n">
         <v>100</v>
@@ -40862,7 +40858,7 @@
         </is>
       </c>
       <c r="C1759" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1759" t="n">
         <v>100</v>
@@ -40885,7 +40881,7 @@
         </is>
       </c>
       <c r="C1760" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1760" t="n">
         <v>100</v>
@@ -40908,7 +40904,7 @@
         </is>
       </c>
       <c r="C1761" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1761" t="n">
         <v>100</v>
@@ -40931,7 +40927,7 @@
         </is>
       </c>
       <c r="C1762" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1762" t="n">
         <v>100</v>
@@ -40954,7 +40950,7 @@
         </is>
       </c>
       <c r="C1763" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1763" t="n">
         <v>100</v>
@@ -40977,7 +40973,7 @@
         </is>
       </c>
       <c r="C1764" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1764" t="n">
         <v>100</v>
@@ -41000,7 +40996,7 @@
         </is>
       </c>
       <c r="C1765" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1765" t="n">
         <v>100</v>
@@ -41023,7 +41019,7 @@
         </is>
       </c>
       <c r="C1766" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1766" t="n">
         <v>100</v>
@@ -41046,7 +41042,7 @@
         </is>
       </c>
       <c r="C1767" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1767" t="n">
         <v>100</v>
@@ -41069,7 +41065,7 @@
         </is>
       </c>
       <c r="C1768" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1768" t="n">
         <v>100</v>
@@ -41092,7 +41088,7 @@
         </is>
       </c>
       <c r="C1769" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1769" t="n">
         <v>100</v>
@@ -41115,7 +41111,7 @@
         </is>
       </c>
       <c r="C1770" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1770" t="n">
         <v>100</v>
@@ -41138,7 +41134,7 @@
         </is>
       </c>
       <c r="C1771" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1771" t="n">
         <v>100</v>
@@ -41161,7 +41157,7 @@
         </is>
       </c>
       <c r="C1772" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1772" t="n">
         <v>100</v>
@@ -41184,7 +41180,7 @@
         </is>
       </c>
       <c r="C1773" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1773" t="n">
         <v>100</v>
@@ -41207,7 +41203,7 @@
         </is>
       </c>
       <c r="C1774" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1774" t="n">
         <v>100</v>
@@ -41230,7 +41226,7 @@
         </is>
       </c>
       <c r="C1775" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1775" t="n">
         <v>100</v>
@@ -41253,7 +41249,7 @@
         </is>
       </c>
       <c r="C1776" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1776" t="n">
         <v>100</v>
@@ -41276,7 +41272,7 @@
         </is>
       </c>
       <c r="C1777" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1777" t="n">
         <v>100</v>
@@ -41299,7 +41295,7 @@
         </is>
       </c>
       <c r="C1778" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1778" t="n">
         <v>100</v>
@@ -41322,7 +41318,7 @@
         </is>
       </c>
       <c r="C1779" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1779" t="n">
         <v>100</v>
@@ -41345,7 +41341,7 @@
         </is>
       </c>
       <c r="C1780" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1780" t="n">
         <v>100</v>
@@ -41368,7 +41364,7 @@
         </is>
       </c>
       <c r="C1781" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1781" t="n">
         <v>100</v>
@@ -41391,7 +41387,7 @@
         </is>
       </c>
       <c r="C1782" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1782" t="n">
         <v>100</v>
@@ -41414,7 +41410,7 @@
         </is>
       </c>
       <c r="C1783" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1783" t="n">
         <v>100</v>
@@ -41437,7 +41433,7 @@
         </is>
       </c>
       <c r="C1784" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1784" t="n">
         <v>100</v>
@@ -41460,7 +41456,7 @@
         </is>
       </c>
       <c r="C1785" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1785" t="n">
         <v>100</v>
@@ -41483,7 +41479,7 @@
         </is>
       </c>
       <c r="C1786" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1786" t="n">
         <v>100</v>
@@ -41506,7 +41502,7 @@
         </is>
       </c>
       <c r="C1787" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1787" t="n">
         <v>100</v>
@@ -41529,7 +41525,7 @@
         </is>
       </c>
       <c r="C1788" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1788" t="n">
         <v>100</v>
@@ -41552,7 +41548,7 @@
         </is>
       </c>
       <c r="C1789" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1789" t="n">
         <v>100</v>
@@ -41575,7 +41571,7 @@
         </is>
       </c>
       <c r="C1790" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1790" t="n">
         <v>100</v>
@@ -41598,7 +41594,7 @@
         </is>
       </c>
       <c r="C1791" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1791" t="n">
         <v>100</v>
@@ -41621,7 +41617,7 @@
         </is>
       </c>
       <c r="C1792" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1792" t="n">
         <v>100</v>
@@ -41644,7 +41640,7 @@
         </is>
       </c>
       <c r="C1793" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1793" t="n">
         <v>100</v>
@@ -41667,7 +41663,7 @@
         </is>
       </c>
       <c r="C1794" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1794" t="n">
         <v>100</v>
@@ -41690,7 +41686,7 @@
         </is>
       </c>
       <c r="C1795" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1795" t="n">
         <v>100</v>
@@ -41713,7 +41709,7 @@
         </is>
       </c>
       <c r="C1796" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1796" t="n">
         <v>100</v>
@@ -41736,7 +41732,7 @@
         </is>
       </c>
       <c r="C1797" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1797" t="n">
         <v>100</v>
@@ -41759,7 +41755,7 @@
         </is>
       </c>
       <c r="C1798" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1798" t="n">
         <v>100</v>
@@ -41782,7 +41778,7 @@
         </is>
       </c>
       <c r="C1799" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1799" t="n">
         <v>100</v>
@@ -41805,7 +41801,7 @@
         </is>
       </c>
       <c r="C1800" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1800" t="n">
         <v>100</v>
@@ -41828,7 +41824,7 @@
         </is>
       </c>
       <c r="C1801" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1801" t="n">
         <v>100</v>
@@ -41851,7 +41847,7 @@
         </is>
       </c>
       <c r="C1802" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1802" t="n">
         <v>100</v>
@@ -41874,7 +41870,7 @@
         </is>
       </c>
       <c r="C1803" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1803" t="n">
         <v>100</v>
@@ -41897,7 +41893,7 @@
         </is>
       </c>
       <c r="C1804" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1804" t="n">
         <v>100</v>
@@ -41920,7 +41916,7 @@
         </is>
       </c>
       <c r="C1805" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1805" t="n">
         <v>100</v>
@@ -41943,7 +41939,7 @@
         </is>
       </c>
       <c r="C1806" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1806" t="n">
         <v>100</v>
@@ -41966,7 +41962,7 @@
         </is>
       </c>
       <c r="C1807" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1807" t="n">
         <v>100</v>
@@ -41989,7 +41985,7 @@
         </is>
       </c>
       <c r="C1808" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1808" t="n">
         <v>100</v>
@@ -42012,7 +42008,7 @@
         </is>
       </c>
       <c r="C1809" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1809" t="n">
         <v>100</v>
@@ -42035,7 +42031,7 @@
         </is>
       </c>
       <c r="C1810" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1810" t="n">
         <v>100</v>
@@ -42058,7 +42054,7 @@
         </is>
       </c>
       <c r="C1811" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1811" t="n">
         <v>100</v>
@@ -42081,7 +42077,7 @@
         </is>
       </c>
       <c r="C1812" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1812" t="n">
         <v>100</v>
@@ -42104,7 +42100,7 @@
         </is>
       </c>
       <c r="C1813" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1813" t="n">
         <v>100</v>
@@ -42127,7 +42123,7 @@
         </is>
       </c>
       <c r="C1814" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1814" t="n">
         <v>100</v>
@@ -42150,7 +42146,7 @@
         </is>
       </c>
       <c r="C1815" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1815" t="n">
         <v>100</v>
@@ -42173,7 +42169,7 @@
         </is>
       </c>
       <c r="C1816" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1816" t="n">
         <v>100</v>
@@ -42196,7 +42192,7 @@
         </is>
       </c>
       <c r="C1817" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1817" t="n">
         <v>100</v>
@@ -42219,7 +42215,7 @@
         </is>
       </c>
       <c r="C1818" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1818" t="n">
         <v>100</v>
@@ -42242,7 +42238,7 @@
         </is>
       </c>
       <c r="C1819" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1819" t="n">
         <v>100</v>
@@ -42265,7 +42261,7 @@
         </is>
       </c>
       <c r="C1820" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1820" t="n">
         <v>100</v>
@@ -42288,7 +42284,7 @@
         </is>
       </c>
       <c r="C1821" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1821" t="n">
         <v>100</v>
@@ -42311,7 +42307,7 @@
         </is>
       </c>
       <c r="C1822" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1822" t="n">
         <v>100</v>
@@ -42334,7 +42330,7 @@
         </is>
       </c>
       <c r="C1823" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1823" t="n">
         <v>100</v>
@@ -42357,7 +42353,7 @@
         </is>
       </c>
       <c r="C1824" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1824" t="n">
         <v>100</v>
@@ -42380,7 +42376,7 @@
         </is>
       </c>
       <c r="C1825" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1825" t="n">
         <v>100</v>
@@ -42403,7 +42399,7 @@
         </is>
       </c>
       <c r="C1826" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1826" t="n">
         <v>100</v>
@@ -42426,7 +42422,7 @@
         </is>
       </c>
       <c r="C1827" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1827" t="n">
         <v>100</v>
@@ -42449,7 +42445,7 @@
         </is>
       </c>
       <c r="C1828" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1828" t="n">
         <v>100</v>
@@ -42472,7 +42468,7 @@
         </is>
       </c>
       <c r="C1829" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1829" t="n">
         <v>100</v>
@@ -42495,7 +42491,7 @@
         </is>
       </c>
       <c r="C1830" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1830" t="n">
         <v>100</v>
@@ -42518,7 +42514,7 @@
         </is>
       </c>
       <c r="C1831" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1831" t="n">
         <v>100</v>
@@ -42541,7 +42537,7 @@
         </is>
       </c>
       <c r="C1832" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1832" t="n">
         <v>100</v>
@@ -42564,7 +42560,7 @@
         </is>
       </c>
       <c r="C1833" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1833" t="n">
         <v>100</v>
@@ -42587,7 +42583,7 @@
         </is>
       </c>
       <c r="C1834" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1834" t="n">
         <v>100</v>
@@ -42610,7 +42606,7 @@
         </is>
       </c>
       <c r="C1835" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1835" t="n">
         <v>100</v>
@@ -42633,7 +42629,7 @@
         </is>
       </c>
       <c r="C1836" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1836" t="n">
         <v>100</v>
@@ -42656,7 +42652,7 @@
         </is>
       </c>
       <c r="C1837" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1837" t="n">
         <v>100</v>
@@ -42679,7 +42675,7 @@
         </is>
       </c>
       <c r="C1838" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1838" t="n">
         <v>100</v>
@@ -42702,7 +42698,7 @@
         </is>
       </c>
       <c r="C1839" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1839" t="n">
         <v>100</v>
@@ -42725,7 +42721,7 @@
         </is>
       </c>
       <c r="C1840" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1840" t="n">
         <v>100</v>
@@ -42748,7 +42744,7 @@
         </is>
       </c>
       <c r="C1841" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1841" t="n">
         <v>100</v>
@@ -42771,7 +42767,7 @@
         </is>
       </c>
       <c r="C1842" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1842" t="n">
         <v>100</v>
@@ -42794,7 +42790,7 @@
         </is>
       </c>
       <c r="C1843" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1843" t="n">
         <v>100</v>
@@ -42817,7 +42813,7 @@
         </is>
       </c>
       <c r="C1844" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1844" t="n">
         <v>100</v>
@@ -42840,7 +42836,7 @@
         </is>
       </c>
       <c r="C1845" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1845" t="n">
         <v>100</v>
@@ -42863,7 +42859,7 @@
         </is>
       </c>
       <c r="C1846" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1846" t="n">
         <v>100</v>
@@ -42886,7 +42882,7 @@
         </is>
       </c>
       <c r="C1847" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1847" t="n">
         <v>100</v>
@@ -42909,7 +42905,7 @@
         </is>
       </c>
       <c r="C1848" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1848" t="n">
         <v>100</v>
@@ -42932,7 +42928,7 @@
         </is>
       </c>
       <c r="C1849" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1849" t="n">
         <v>100</v>
@@ -42955,7 +42951,7 @@
         </is>
       </c>
       <c r="C1850" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1850" t="n">
         <v>100</v>
@@ -42978,7 +42974,7 @@
         </is>
       </c>
       <c r="C1851" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1851" t="n">
         <v>100</v>
@@ -43001,7 +42997,7 @@
         </is>
       </c>
       <c r="C1852" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1852" t="n">
         <v>100</v>
@@ -43024,7 +43020,7 @@
         </is>
       </c>
       <c r="C1853" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1853" t="n">
         <v>100</v>
@@ -43047,7 +43043,7 @@
         </is>
       </c>
       <c r="C1854" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1854" t="n">
         <v>100</v>
@@ -43070,7 +43066,7 @@
         </is>
       </c>
       <c r="C1855" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1855" t="n">
         <v>100</v>
@@ -43093,7 +43089,7 @@
         </is>
       </c>
       <c r="C1856" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1856" t="n">
         <v>100</v>
@@ -43116,7 +43112,7 @@
         </is>
       </c>
       <c r="C1857" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1857" t="n">
         <v>100</v>
@@ -43139,7 +43135,7 @@
         </is>
       </c>
       <c r="C1858" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1858" t="n">
         <v>100</v>
@@ -43162,7 +43158,7 @@
         </is>
       </c>
       <c r="C1859" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1859" t="n">
         <v>100</v>
@@ -43185,7 +43181,7 @@
         </is>
       </c>
       <c r="C1860" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1860" t="n">
         <v>100</v>
@@ -43208,7 +43204,7 @@
         </is>
       </c>
       <c r="C1861" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1861" t="n">
         <v>100</v>
@@ -43231,7 +43227,7 @@
         </is>
       </c>
       <c r="C1862" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1862" t="n">
         <v>100</v>
@@ -43254,7 +43250,7 @@
         </is>
       </c>
       <c r="C1863" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1863" t="n">
         <v>100</v>
@@ -43277,7 +43273,7 @@
         </is>
       </c>
       <c r="C1864" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1864" t="n">
         <v>100</v>
@@ -43300,7 +43296,7 @@
         </is>
       </c>
       <c r="C1865" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1865" t="n">
         <v>100</v>
@@ -43323,7 +43319,7 @@
         </is>
       </c>
       <c r="C1866" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1866" t="n">
         <v>100</v>
@@ -43346,7 +43342,7 @@
         </is>
       </c>
       <c r="C1867" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1867" t="n">
         <v>100</v>
@@ -43369,7 +43365,7 @@
         </is>
       </c>
       <c r="C1868" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1868" t="n">
         <v>100</v>
@@ -43392,7 +43388,7 @@
         </is>
       </c>
       <c r="C1869" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1869" t="n">
         <v>100</v>
@@ -43415,7 +43411,7 @@
         </is>
       </c>
       <c r="C1870" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1870" t="n">
         <v>100</v>
@@ -43438,7 +43434,7 @@
         </is>
       </c>
       <c r="C1871" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1871" t="n">
         <v>100</v>
@@ -43461,7 +43457,7 @@
         </is>
       </c>
       <c r="C1872" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1872" t="n">
         <v>100</v>
@@ -43484,7 +43480,7 @@
         </is>
       </c>
       <c r="C1873" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1873" t="n">
         <v>100</v>
@@ -43507,7 +43503,7 @@
         </is>
       </c>
       <c r="C1874" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1874" t="n">
         <v>100</v>
@@ -43530,7 +43526,7 @@
         </is>
       </c>
       <c r="C1875" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1875" t="n">
         <v>100</v>
@@ -43553,7 +43549,7 @@
         </is>
       </c>
       <c r="C1876" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1876" t="n">
         <v>100</v>
@@ -43576,7 +43572,7 @@
         </is>
       </c>
       <c r="C1877" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1877" t="n">
         <v>100</v>
@@ -43599,7 +43595,7 @@
         </is>
       </c>
       <c r="C1878" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1878" t="n">
         <v>100</v>
@@ -43622,7 +43618,7 @@
         </is>
       </c>
       <c r="C1879" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1879" t="n">
         <v>100</v>
@@ -43645,7 +43641,7 @@
         </is>
       </c>
       <c r="C1880" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1880" t="n">
         <v>100</v>
@@ -43668,7 +43664,7 @@
         </is>
       </c>
       <c r="C1881" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1881" t="n">
         <v>100</v>
@@ -43691,7 +43687,7 @@
         </is>
       </c>
       <c r="C1882" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1882" t="n">
         <v>100</v>
@@ -43714,7 +43710,7 @@
         </is>
       </c>
       <c r="C1883" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1883" t="n">
         <v>100</v>
@@ -43737,7 +43733,7 @@
         </is>
       </c>
       <c r="C1884" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1884" t="n">
         <v>100</v>
@@ -43760,7 +43756,7 @@
         </is>
       </c>
       <c r="C1885" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1885" t="n">
         <v>100</v>
@@ -43783,7 +43779,7 @@
         </is>
       </c>
       <c r="C1886" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1886" t="n">
         <v>100</v>
@@ -43806,7 +43802,7 @@
         </is>
       </c>
       <c r="C1887" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1887" t="n">
         <v>100</v>
@@ -43829,7 +43825,7 @@
         </is>
       </c>
       <c r="C1888" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1888" t="n">
         <v>100</v>
@@ -43852,7 +43848,7 @@
         </is>
       </c>
       <c r="C1889" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1889" t="n">
         <v>100</v>
@@ -43875,7 +43871,7 @@
         </is>
       </c>
       <c r="C1890" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1890" t="n">
         <v>100</v>
@@ -43898,7 +43894,7 @@
         </is>
       </c>
       <c r="C1891" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1891" t="n">
         <v>100</v>
@@ -43921,7 +43917,7 @@
         </is>
       </c>
       <c r="C1892" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1892" t="n">
         <v>100</v>
@@ -43944,7 +43940,7 @@
         </is>
       </c>
       <c r="C1893" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1893" t="n">
         <v>100</v>
@@ -43967,7 +43963,7 @@
         </is>
       </c>
       <c r="C1894" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1894" t="n">
         <v>100</v>
@@ -43990,7 +43986,7 @@
         </is>
       </c>
       <c r="C1895" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1895" t="n">
         <v>100</v>
@@ -44013,7 +44009,7 @@
         </is>
       </c>
       <c r="C1896" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1896" t="n">
         <v>100</v>
@@ -44036,7 +44032,7 @@
         </is>
       </c>
       <c r="C1897" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1897" t="n">
         <v>100</v>
@@ -44059,7 +44055,7 @@
         </is>
       </c>
       <c r="C1898" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1898" t="n">
         <v>100</v>
@@ -44082,7 +44078,7 @@
         </is>
       </c>
       <c r="C1899" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1899" t="n">
         <v>100</v>
@@ -44105,7 +44101,7 @@
         </is>
       </c>
       <c r="C1900" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1900" t="n">
         <v>100</v>
@@ -44128,7 +44124,7 @@
         </is>
       </c>
       <c r="C1901" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1901" t="n">
         <v>100</v>
@@ -44151,7 +44147,7 @@
         </is>
       </c>
       <c r="C1902" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1902" t="n">
         <v>100</v>
@@ -44174,7 +44170,7 @@
         </is>
       </c>
       <c r="C1903" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1903" t="n">
         <v>100</v>
@@ -44197,7 +44193,7 @@
         </is>
       </c>
       <c r="C1904" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1904" t="n">
         <v>100</v>
@@ -44220,7 +44216,7 @@
         </is>
       </c>
       <c r="C1905" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1905" t="n">
         <v>100</v>
@@ -44243,7 +44239,7 @@
         </is>
       </c>
       <c r="C1906" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1906" t="n">
         <v>100</v>
@@ -44266,7 +44262,7 @@
         </is>
       </c>
       <c r="C1907" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1907" t="n">
         <v>100</v>
@@ -44289,7 +44285,7 @@
         </is>
       </c>
       <c r="C1908" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1908" t="n">
         <v>100</v>
@@ -44312,7 +44308,7 @@
         </is>
       </c>
       <c r="C1909" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1909" t="n">
         <v>100</v>
@@ -44335,7 +44331,7 @@
         </is>
       </c>
       <c r="C1910" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1910" t="n">
         <v>100</v>
@@ -44358,7 +44354,7 @@
         </is>
       </c>
       <c r="C1911" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1911" t="n">
         <v>100</v>
@@ -44381,7 +44377,7 @@
         </is>
       </c>
       <c r="C1912" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1912" t="n">
         <v>100</v>
@@ -44404,7 +44400,7 @@
         </is>
       </c>
       <c r="C1913" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1913" t="n">
         <v>100</v>
@@ -44427,7 +44423,7 @@
         </is>
       </c>
       <c r="C1914" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1914" t="n">
         <v>100</v>
@@ -44450,7 +44446,7 @@
         </is>
       </c>
       <c r="C1915" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1915" t="n">
         <v>100</v>
@@ -44473,7 +44469,7 @@
         </is>
       </c>
       <c r="C1916" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1916" t="n">
         <v>100</v>
@@ -44496,7 +44492,7 @@
         </is>
       </c>
       <c r="C1917" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1917" t="n">
         <v>100</v>
@@ -44519,7 +44515,7 @@
         </is>
       </c>
       <c r="C1918" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1918" t="n">
         <v>100</v>
@@ -44542,7 +44538,7 @@
         </is>
       </c>
       <c r="C1919" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1919" t="n">
         <v>100</v>
@@ -44565,7 +44561,7 @@
         </is>
       </c>
       <c r="C1920" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1920" t="n">
         <v>100</v>
@@ -44588,7 +44584,7 @@
         </is>
       </c>
       <c r="C1921" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1921" t="n">
         <v>100</v>
@@ -44611,7 +44607,7 @@
         </is>
       </c>
       <c r="C1922" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1922" t="n">
         <v>100</v>
@@ -44634,7 +44630,7 @@
         </is>
       </c>
       <c r="C1923" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1923" t="n">
         <v>100</v>
@@ -44657,7 +44653,7 @@
         </is>
       </c>
       <c r="C1924" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1924" t="n">
         <v>100</v>
@@ -44680,7 +44676,7 @@
         </is>
       </c>
       <c r="C1925" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1925" t="n">
         <v>100</v>
@@ -44703,7 +44699,7 @@
         </is>
       </c>
       <c r="C1926" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1926" t="n">
         <v>100</v>
@@ -44726,7 +44722,7 @@
         </is>
       </c>
       <c r="C1927" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1927" t="n">
         <v>100</v>
@@ -44749,7 +44745,7 @@
         </is>
       </c>
       <c r="C1928" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1928" t="n">
         <v>100</v>
@@ -44772,7 +44768,7 @@
         </is>
       </c>
       <c r="C1929" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1929" t="n">
         <v>100</v>
@@ -44795,7 +44791,7 @@
         </is>
       </c>
       <c r="C1930" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1930" t="n">
         <v>100</v>
@@ -44818,7 +44814,7 @@
         </is>
       </c>
       <c r="C1931" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1931" t="n">
         <v>100</v>
@@ -44841,7 +44837,7 @@
         </is>
       </c>
       <c r="C1932" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1932" t="n">
         <v>100</v>
@@ -44864,7 +44860,7 @@
         </is>
       </c>
       <c r="C1933" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1933" t="n">
         <v>100</v>
@@ -44887,7 +44883,7 @@
         </is>
       </c>
       <c r="C1934" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1934" t="n">
         <v>100</v>
@@ -44910,7 +44906,7 @@
         </is>
       </c>
       <c r="C1935" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1935" t="n">
         <v>100</v>
@@ -44933,7 +44929,7 @@
         </is>
       </c>
       <c r="C1936" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1936" t="n">
         <v>100</v>
@@ -44956,7 +44952,7 @@
         </is>
       </c>
       <c r="C1937" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1937" t="n">
         <v>100</v>
@@ -44979,7 +44975,7 @@
         </is>
       </c>
       <c r="C1938" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1938" t="n">
         <v>100</v>
@@ -45002,7 +44998,7 @@
         </is>
       </c>
       <c r="C1939" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1939" t="n">
         <v>100</v>
@@ -45025,7 +45021,7 @@
         </is>
       </c>
       <c r="C1940" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1940" t="n">
         <v>100</v>
@@ -45048,7 +45044,7 @@
         </is>
       </c>
       <c r="C1941" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1941" t="n">
         <v>100</v>
@@ -45071,7 +45067,7 @@
         </is>
       </c>
       <c r="C1942" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1942" t="n">
         <v>100</v>
@@ -45094,7 +45090,7 @@
         </is>
       </c>
       <c r="C1943" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1943" t="n">
         <v>100</v>
@@ -45117,7 +45113,7 @@
         </is>
       </c>
       <c r="C1944" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1944" t="n">
         <v>100</v>
@@ -45140,7 +45136,7 @@
         </is>
       </c>
       <c r="C1945" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1945" t="n">
         <v>100</v>
@@ -45163,7 +45159,7 @@
         </is>
       </c>
       <c r="C1946" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1946" t="n">
         <v>100</v>
@@ -45186,7 +45182,7 @@
         </is>
       </c>
       <c r="C1947" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1947" t="n">
         <v>100</v>
@@ -45209,7 +45205,7 @@
         </is>
       </c>
       <c r="C1948" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1948" t="n">
         <v>100</v>
@@ -45232,7 +45228,7 @@
         </is>
       </c>
       <c r="C1949" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1949" t="n">
         <v>100</v>
@@ -45255,7 +45251,7 @@
         </is>
       </c>
       <c r="C1950" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1950" t="n">
         <v>100</v>
@@ -45278,7 +45274,7 @@
         </is>
       </c>
       <c r="C1951" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1951" t="n">
         <v>100</v>
@@ -45301,7 +45297,7 @@
         </is>
       </c>
       <c r="C1952" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1952" t="n">
         <v>100</v>
@@ -45324,7 +45320,7 @@
         </is>
       </c>
       <c r="C1953" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1953" t="n">
         <v>100</v>
@@ -45347,7 +45343,7 @@
         </is>
       </c>
       <c r="C1954" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1954" t="n">
         <v>100</v>
@@ -45370,7 +45366,7 @@
         </is>
       </c>
       <c r="C1955" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1955" t="n">
         <v>100</v>
@@ -45393,7 +45389,7 @@
         </is>
       </c>
       <c r="C1956" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1956" t="n">
         <v>100</v>
@@ -45416,7 +45412,7 @@
         </is>
       </c>
       <c r="C1957" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1957" t="n">
         <v>100</v>
@@ -45439,7 +45435,7 @@
         </is>
       </c>
       <c r="C1958" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1958" t="n">
         <v>100</v>
@@ -45462,7 +45458,7 @@
         </is>
       </c>
       <c r="C1959" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1959" t="n">
         <v>100</v>
@@ -45485,7 +45481,7 @@
         </is>
       </c>
       <c r="C1960" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1960" t="n">
         <v>100</v>
@@ -45508,7 +45504,7 @@
         </is>
       </c>
       <c r="C1961" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1961" t="n">
         <v>100</v>
@@ -45531,7 +45527,7 @@
         </is>
       </c>
       <c r="C1962" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1962" t="n">
         <v>100</v>
@@ -45554,7 +45550,7 @@
         </is>
       </c>
       <c r="C1963" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1963" t="n">
         <v>100</v>
@@ -45577,7 +45573,7 @@
         </is>
       </c>
       <c r="C1964" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1964" t="n">
         <v>100</v>
@@ -45600,7 +45596,7 @@
         </is>
       </c>
       <c r="C1965" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1965" t="n">
         <v>100</v>
@@ -45623,7 +45619,7 @@
         </is>
       </c>
       <c r="C1966" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1966" t="n">
         <v>100</v>
@@ -45646,7 +45642,7 @@
         </is>
       </c>
       <c r="C1967" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1967" t="n">
         <v>100</v>
@@ -45669,7 +45665,7 @@
         </is>
       </c>
       <c r="C1968" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1968" t="n">
         <v>100</v>
@@ -45692,7 +45688,7 @@
         </is>
       </c>
       <c r="C1969" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1969" t="n">
         <v>100</v>
@@ -45715,7 +45711,7 @@
         </is>
       </c>
       <c r="C1970" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1970" t="n">
         <v>100</v>
@@ -45738,7 +45734,7 @@
         </is>
       </c>
       <c r="C1971" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1971" t="n">
         <v>100</v>
@@ -45761,7 +45757,7 @@
         </is>
       </c>
       <c r="C1972" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1972" t="n">
         <v>100</v>
@@ -45784,7 +45780,7 @@
         </is>
       </c>
       <c r="C1973" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1973" t="n">
         <v>100</v>
@@ -45807,7 +45803,7 @@
         </is>
       </c>
       <c r="C1974" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1974" t="n">
         <v>100</v>
@@ -45830,7 +45826,7 @@
         </is>
       </c>
       <c r="C1975" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1975" t="n">
         <v>100</v>
@@ -45853,7 +45849,7 @@
         </is>
       </c>
       <c r="C1976" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1976" t="n">
         <v>100</v>
@@ -45876,7 +45872,7 @@
         </is>
       </c>
       <c r="C1977" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1977" t="n">
         <v>100</v>
@@ -45899,7 +45895,7 @@
         </is>
       </c>
       <c r="C1978" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1978" t="n">
         <v>100</v>
@@ -45922,7 +45918,7 @@
         </is>
       </c>
       <c r="C1979" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1979" t="n">
         <v>100</v>
@@ -45945,7 +45941,7 @@
         </is>
       </c>
       <c r="C1980" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1980" t="n">
         <v>100</v>
@@ -45968,7 +45964,7 @@
         </is>
       </c>
       <c r="C1981" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1981" t="n">
         <v>100</v>
@@ -45991,7 +45987,7 @@
         </is>
       </c>
       <c r="C1982" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1982" t="n">
         <v>100</v>
@@ -46014,7 +46010,7 @@
         </is>
       </c>
       <c r="C1983" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1983" t="n">
         <v>100</v>
@@ -46037,7 +46033,7 @@
         </is>
       </c>
       <c r="C1984" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1984" t="n">
         <v>100</v>
@@ -46060,7 +46056,7 @@
         </is>
       </c>
       <c r="C1985" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1985" t="n">
         <v>100</v>
@@ -46083,7 +46079,7 @@
         </is>
       </c>
       <c r="C1986" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1986" t="n">
         <v>100</v>
@@ -46106,7 +46102,7 @@
         </is>
       </c>
       <c r="C1987" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1987" t="n">
         <v>100</v>
@@ -46129,7 +46125,7 @@
         </is>
       </c>
       <c r="C1988" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1988" t="n">
         <v>100</v>
@@ -46152,7 +46148,7 @@
         </is>
       </c>
       <c r="C1989" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1989" t="n">
         <v>100</v>
@@ -46175,7 +46171,7 @@
         </is>
       </c>
       <c r="C1990" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1990" t="n">
         <v>100</v>
@@ -46198,7 +46194,7 @@
         </is>
       </c>
       <c r="C1991" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1991" t="n">
         <v>100</v>
@@ -46221,7 +46217,7 @@
         </is>
       </c>
       <c r="C1992" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1992" t="n">
         <v>100</v>
@@ -46244,7 +46240,7 @@
         </is>
       </c>
       <c r="C1993" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1993" t="n">
         <v>100</v>
@@ -46267,7 +46263,7 @@
         </is>
       </c>
       <c r="C1994" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1994" t="n">
         <v>100</v>
@@ -46290,7 +46286,7 @@
         </is>
       </c>
       <c r="C1995" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1995" t="n">
         <v>100</v>
@@ -46313,7 +46309,7 @@
         </is>
       </c>
       <c r="C1996" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1996" t="n">
         <v>100</v>
@@ -46336,7 +46332,7 @@
         </is>
       </c>
       <c r="C1997" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1997" t="n">
         <v>100</v>
@@ -46359,7 +46355,7 @@
         </is>
       </c>
       <c r="C1998" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1998" t="n">
         <v>100</v>
@@ -46382,7 +46378,7 @@
         </is>
       </c>
       <c r="C1999" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D1999" t="n">
         <v>100</v>
@@ -46405,7 +46401,7 @@
         </is>
       </c>
       <c r="C2000" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2000" t="n">
         <v>100</v>
@@ -46428,7 +46424,7 @@
         </is>
       </c>
       <c r="C2001" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2001" t="n">
         <v>100</v>
@@ -46451,7 +46447,7 @@
         </is>
       </c>
       <c r="C2002" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2002" t="n">
         <v>100</v>
@@ -46474,7 +46470,7 @@
         </is>
       </c>
       <c r="C2003" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2003" t="n">
         <v>100</v>
@@ -46497,7 +46493,7 @@
         </is>
       </c>
       <c r="C2004" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2004" t="n">
         <v>100</v>
@@ -46520,7 +46516,7 @@
         </is>
       </c>
       <c r="C2005" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2005" t="n">
         <v>100</v>
@@ -46543,7 +46539,7 @@
         </is>
       </c>
       <c r="C2006" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2006" t="n">
         <v>100</v>
@@ -46566,7 +46562,7 @@
         </is>
       </c>
       <c r="C2007" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2007" t="n">
         <v>100</v>
@@ -46589,7 +46585,7 @@
         </is>
       </c>
       <c r="C2008" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2008" t="n">
         <v>100</v>
@@ -46612,7 +46608,7 @@
         </is>
       </c>
       <c r="C2009" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2009" t="n">
         <v>100</v>
@@ -46635,7 +46631,7 @@
         </is>
       </c>
       <c r="C2010" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2010" t="n">
         <v>100</v>
@@ -46658,7 +46654,7 @@
         </is>
       </c>
       <c r="C2011" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2011" t="n">
         <v>100</v>
@@ -46681,7 +46677,7 @@
         </is>
       </c>
       <c r="C2012" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2012" t="n">
         <v>100</v>
@@ -46704,7 +46700,7 @@
         </is>
       </c>
       <c r="C2013" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2013" t="n">
         <v>100</v>
@@ -46727,7 +46723,7 @@
         </is>
       </c>
       <c r="C2014" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2014" t="n">
         <v>100</v>
@@ -46750,7 +46746,7 @@
         </is>
       </c>
       <c r="C2015" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2015" t="n">
         <v>100</v>
@@ -46773,7 +46769,7 @@
         </is>
       </c>
       <c r="C2016" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2016" t="n">
         <v>100</v>
@@ -46796,7 +46792,7 @@
         </is>
       </c>
       <c r="C2017" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2017" t="n">
         <v>100</v>
@@ -46819,7 +46815,7 @@
         </is>
       </c>
       <c r="C2018" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2018" t="n">
         <v>100</v>
@@ -46842,7 +46838,7 @@
         </is>
       </c>
       <c r="C2019" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2019" t="n">
         <v>100</v>
@@ -46865,7 +46861,7 @@
         </is>
       </c>
       <c r="C2020" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2020" t="n">
         <v>100</v>
@@ -46888,7 +46884,7 @@
         </is>
       </c>
       <c r="C2021" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2021" t="n">
         <v>100</v>
@@ -46911,7 +46907,7 @@
         </is>
       </c>
       <c r="C2022" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2022" t="n">
         <v>100</v>
@@ -46934,7 +46930,7 @@
         </is>
       </c>
       <c r="C2023" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2023" t="n">
         <v>100</v>
@@ -46957,7 +46953,7 @@
         </is>
       </c>
       <c r="C2024" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2024" t="n">
         <v>100</v>
@@ -46980,7 +46976,7 @@
         </is>
       </c>
       <c r="C2025" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2025" t="n">
         <v>100</v>
@@ -47003,7 +46999,7 @@
         </is>
       </c>
       <c r="C2026" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2026" t="n">
         <v>100</v>
@@ -47026,7 +47022,7 @@
         </is>
       </c>
       <c r="C2027" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2027" t="n">
         <v>100</v>
@@ -47049,7 +47045,7 @@
         </is>
       </c>
       <c r="C2028" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2028" t="n">
         <v>100</v>
@@ -47072,7 +47068,7 @@
         </is>
       </c>
       <c r="C2029" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2029" t="n">
         <v>100</v>
@@ -47095,7 +47091,7 @@
         </is>
       </c>
       <c r="C2030" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2030" t="n">
         <v>100</v>
@@ -47118,7 +47114,7 @@
         </is>
       </c>
       <c r="C2031" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2031" t="n">
         <v>100</v>
@@ -47141,7 +47137,7 @@
         </is>
       </c>
       <c r="C2032" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2032" t="n">
         <v>100</v>
@@ -47164,7 +47160,7 @@
         </is>
       </c>
       <c r="C2033" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2033" t="n">
         <v>100</v>
@@ -47187,7 +47183,7 @@
         </is>
       </c>
       <c r="C2034" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2034" t="n">
         <v>100</v>
@@ -47210,7 +47206,7 @@
         </is>
       </c>
       <c r="C2035" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2035" t="n">
         <v>100</v>
@@ -47233,7 +47229,7 @@
         </is>
       </c>
       <c r="C2036" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2036" t="n">
         <v>100</v>
@@ -47256,7 +47252,7 @@
         </is>
       </c>
       <c r="C2037" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2037" t="n">
         <v>100</v>
@@ -47279,7 +47275,7 @@
         </is>
       </c>
       <c r="C2038" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2038" t="n">
         <v>100</v>
@@ -47302,7 +47298,7 @@
         </is>
       </c>
       <c r="C2039" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2039" t="n">
         <v>100</v>
@@ -47325,7 +47321,7 @@
         </is>
       </c>
       <c r="C2040" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2040" t="n">
         <v>100</v>
@@ -47348,7 +47344,7 @@
         </is>
       </c>
       <c r="C2041" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2041" t="n">
         <v>100</v>
@@ -47371,7 +47367,7 @@
         </is>
       </c>
       <c r="C2042" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2042" t="n">
         <v>100</v>
@@ -47394,7 +47390,7 @@
         </is>
       </c>
       <c r="C2043" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2043" t="n">
         <v>100</v>
@@ -47417,7 +47413,7 @@
         </is>
       </c>
       <c r="C2044" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2044" t="n">
         <v>100</v>
@@ -47440,7 +47436,7 @@
         </is>
       </c>
       <c r="C2045" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2045" t="n">
         <v>100</v>
@@ -47463,7 +47459,7 @@
         </is>
       </c>
       <c r="C2046" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2046" t="n">
         <v>100</v>
@@ -47486,7 +47482,7 @@
         </is>
       </c>
       <c r="C2047" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2047" t="n">
         <v>100</v>
@@ -47509,7 +47505,7 @@
         </is>
       </c>
       <c r="C2048" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2048" t="n">
         <v>100</v>
@@ -47532,7 +47528,7 @@
         </is>
       </c>
       <c r="C2049" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2049" t="n">
         <v>100</v>
@@ -47555,7 +47551,7 @@
         </is>
       </c>
       <c r="C2050" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2050" t="n">
         <v>100</v>
@@ -47578,7 +47574,7 @@
         </is>
       </c>
       <c r="C2051" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2051" t="n">
         <v>100</v>
@@ -47601,7 +47597,7 @@
         </is>
       </c>
       <c r="C2052" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2052" t="n">
         <v>100</v>
@@ -47624,7 +47620,7 @@
         </is>
       </c>
       <c r="C2053" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2053" t="n">
         <v>100</v>
@@ -47647,7 +47643,7 @@
         </is>
       </c>
       <c r="C2054" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2054" t="n">
         <v>100</v>
@@ -47670,7 +47666,7 @@
         </is>
       </c>
       <c r="C2055" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2055" t="n">
         <v>100</v>
@@ -47693,7 +47689,7 @@
         </is>
       </c>
       <c r="C2056" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2056" t="n">
         <v>100</v>
@@ -47716,7 +47712,7 @@
         </is>
       </c>
       <c r="C2057" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2057" t="n">
         <v>100</v>
@@ -47739,7 +47735,7 @@
         </is>
       </c>
       <c r="C2058" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2058" t="n">
         <v>100</v>
@@ -47762,7 +47758,7 @@
         </is>
       </c>
       <c r="C2059" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2059" t="n">
         <v>100</v>
@@ -47785,7 +47781,7 @@
         </is>
       </c>
       <c r="C2060" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2060" t="n">
         <v>100</v>
@@ -47808,7 +47804,7 @@
         </is>
       </c>
       <c r="C2061" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2061" t="n">
         <v>100</v>
@@ -47831,7 +47827,7 @@
         </is>
       </c>
       <c r="C2062" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2062" t="n">
         <v>100</v>
@@ -47854,7 +47850,7 @@
         </is>
       </c>
       <c r="C2063" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2063" t="n">
         <v>100</v>
@@ -47877,7 +47873,7 @@
         </is>
       </c>
       <c r="C2064" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2064" t="n">
         <v>100</v>
@@ -47900,7 +47896,7 @@
         </is>
       </c>
       <c r="C2065" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2065" t="n">
         <v>100</v>
@@ -47923,7 +47919,7 @@
         </is>
       </c>
       <c r="C2066" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2066" t="n">
         <v>100</v>
@@ -47946,7 +47942,7 @@
         </is>
       </c>
       <c r="C2067" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2067" t="n">
         <v>100</v>
@@ -47969,7 +47965,7 @@
         </is>
       </c>
       <c r="C2068" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2068" t="n">
         <v>100</v>
@@ -47992,7 +47988,7 @@
         </is>
       </c>
       <c r="C2069" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2069" t="n">
         <v>100</v>
@@ -48015,7 +48011,7 @@
         </is>
       </c>
       <c r="C2070" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2070" t="n">
         <v>100</v>
@@ -48038,7 +48034,7 @@
         </is>
       </c>
       <c r="C2071" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2071" t="n">
         <v>100</v>
@@ -48061,7 +48057,7 @@
         </is>
       </c>
       <c r="C2072" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2072" t="n">
         <v>100</v>
@@ -48084,7 +48080,7 @@
         </is>
       </c>
       <c r="C2073" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2073" t="n">
         <v>100</v>
@@ -48107,7 +48103,7 @@
         </is>
       </c>
       <c r="C2074" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2074" t="n">
         <v>100</v>
@@ -48130,7 +48126,7 @@
         </is>
       </c>
       <c r="C2075" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2075" t="n">
         <v>100</v>
@@ -48153,7 +48149,7 @@
         </is>
       </c>
       <c r="C2076" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2076" t="n">
         <v>100</v>
@@ -48176,7 +48172,7 @@
         </is>
       </c>
       <c r="C2077" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2077" t="n">
         <v>100</v>
@@ -48199,7 +48195,7 @@
         </is>
       </c>
       <c r="C2078" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2078" t="n">
         <v>100</v>
@@ -48222,7 +48218,7 @@
         </is>
       </c>
       <c r="C2079" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2079" t="n">
         <v>100</v>
@@ -48245,7 +48241,7 @@
         </is>
       </c>
       <c r="C2080" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2080" t="n">
         <v>100</v>
@@ -48268,7 +48264,7 @@
         </is>
       </c>
       <c r="C2081" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2081" t="n">
         <v>100</v>
@@ -48291,7 +48287,7 @@
         </is>
       </c>
       <c r="C2082" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2082" t="n">
         <v>100</v>
@@ -48314,7 +48310,7 @@
         </is>
       </c>
       <c r="C2083" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2083" t="n">
         <v>100</v>
@@ -48337,7 +48333,7 @@
         </is>
       </c>
       <c r="C2084" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2084" t="n">
         <v>100</v>
@@ -48360,7 +48356,7 @@
         </is>
       </c>
       <c r="C2085" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2085" t="n">
         <v>100</v>
@@ -48383,7 +48379,7 @@
         </is>
       </c>
       <c r="C2086" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2086" t="n">
         <v>100</v>
@@ -48406,7 +48402,7 @@
         </is>
       </c>
       <c r="C2087" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2087" t="n">
         <v>100</v>
@@ -48429,7 +48425,7 @@
         </is>
       </c>
       <c r="C2088" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2088" t="n">
         <v>100</v>
@@ -48452,7 +48448,7 @@
         </is>
       </c>
       <c r="C2089" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2089" t="n">
         <v>100</v>
@@ -48475,7 +48471,7 @@
         </is>
       </c>
       <c r="C2090" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2090" t="n">
         <v>100</v>
@@ -48498,7 +48494,7 @@
         </is>
       </c>
       <c r="C2091" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2091" t="n">
         <v>100</v>
@@ -48521,7 +48517,7 @@
         </is>
       </c>
       <c r="C2092" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2092" t="n">
         <v>100</v>
@@ -48544,7 +48540,7 @@
         </is>
       </c>
       <c r="C2093" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2093" t="n">
         <v>100</v>
@@ -48567,7 +48563,7 @@
         </is>
       </c>
       <c r="C2094" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2094" t="n">
         <v>100</v>
@@ -48590,7 +48586,7 @@
         </is>
       </c>
       <c r="C2095" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2095" t="n">
         <v>100</v>
@@ -48613,7 +48609,7 @@
         </is>
       </c>
       <c r="C2096" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2096" t="n">
         <v>100</v>
@@ -48636,7 +48632,7 @@
         </is>
       </c>
       <c r="C2097" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2097" t="n">
         <v>100</v>
@@ -48659,7 +48655,7 @@
         </is>
       </c>
       <c r="C2098" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2098" t="n">
         <v>100</v>
@@ -48682,7 +48678,7 @@
         </is>
       </c>
       <c r="C2099" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2099" t="n">
         <v>100</v>
@@ -48705,7 +48701,7 @@
         </is>
       </c>
       <c r="C2100" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2100" t="n">
         <v>100</v>
@@ -48728,7 +48724,7 @@
         </is>
       </c>
       <c r="C2101" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2101" t="n">
         <v>100</v>
@@ -48751,7 +48747,7 @@
         </is>
       </c>
       <c r="C2102" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2102" t="n">
         <v>100</v>
@@ -48774,7 +48770,7 @@
         </is>
       </c>
       <c r="C2103" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2103" t="n">
         <v>100</v>
@@ -48797,7 +48793,7 @@
         </is>
       </c>
       <c r="C2104" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2104" t="n">
         <v>100</v>
@@ -48820,7 +48816,7 @@
         </is>
       </c>
       <c r="C2105" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2105" t="n">
         <v>100</v>
@@ -48843,7 +48839,7 @@
         </is>
       </c>
       <c r="C2106" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2106" t="n">
         <v>100</v>
@@ -48866,7 +48862,7 @@
         </is>
       </c>
       <c r="C2107" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2107" t="n">
         <v>100</v>
@@ -48889,7 +48885,7 @@
         </is>
       </c>
       <c r="C2108" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2108" t="n">
         <v>100</v>
@@ -48912,7 +48908,7 @@
         </is>
       </c>
       <c r="C2109" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2109" t="n">
         <v>100</v>
@@ -48935,7 +48931,7 @@
         </is>
       </c>
       <c r="C2110" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2110" t="n">
         <v>100</v>
@@ -48958,7 +48954,7 @@
         </is>
       </c>
       <c r="C2111" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2111" t="n">
         <v>100</v>
@@ -48981,7 +48977,7 @@
         </is>
       </c>
       <c r="C2112" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2112" t="n">
         <v>100</v>
@@ -49004,7 +49000,7 @@
         </is>
       </c>
       <c r="C2113" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2113" t="n">
         <v>100</v>
@@ -49027,7 +49023,7 @@
         </is>
       </c>
       <c r="C2114" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2114" t="n">
         <v>100</v>
@@ -49050,7 +49046,7 @@
         </is>
       </c>
       <c r="C2115" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2115" t="n">
         <v>100</v>
@@ -49073,7 +49069,7 @@
         </is>
       </c>
       <c r="C2116" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2116" t="n">
         <v>100</v>
@@ -49096,7 +49092,7 @@
         </is>
       </c>
       <c r="C2117" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2117" t="n">
         <v>100</v>
@@ -49119,7 +49115,7 @@
         </is>
       </c>
       <c r="C2118" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2118" t="n">
         <v>100</v>
@@ -49142,7 +49138,7 @@
         </is>
       </c>
       <c r="C2119" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2119" t="n">
         <v>100</v>
@@ -49165,7 +49161,7 @@
         </is>
       </c>
       <c r="C2120" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2120" t="n">
         <v>100</v>
@@ -49188,7 +49184,7 @@
         </is>
       </c>
       <c r="C2121" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2121" t="n">
         <v>100</v>
@@ -49211,7 +49207,7 @@
         </is>
       </c>
       <c r="C2122" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2122" t="n">
         <v>100</v>
@@ -49234,7 +49230,7 @@
         </is>
       </c>
       <c r="C2123" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2123" t="n">
         <v>100</v>
@@ -49257,7 +49253,7 @@
         </is>
       </c>
       <c r="C2124" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2124" t="n">
         <v>100</v>
@@ -49280,7 +49276,7 @@
         </is>
       </c>
       <c r="C2125" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2125" t="n">
         <v>100</v>
@@ -49303,7 +49299,7 @@
         </is>
       </c>
       <c r="C2126" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2126" t="n">
         <v>100</v>
@@ -49326,7 +49322,7 @@
         </is>
       </c>
       <c r="C2127" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2127" t="n">
         <v>100</v>
@@ -49349,7 +49345,7 @@
         </is>
       </c>
       <c r="C2128" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2128" t="n">
         <v>100</v>
@@ -49372,7 +49368,7 @@
         </is>
       </c>
       <c r="C2129" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2129" t="n">
         <v>100</v>
@@ -49395,7 +49391,7 @@
         </is>
       </c>
       <c r="C2130" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2130" t="n">
         <v>100</v>
@@ -49418,7 +49414,7 @@
         </is>
       </c>
       <c r="C2131" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2131" t="n">
         <v>100</v>
@@ -49441,7 +49437,7 @@
         </is>
       </c>
       <c r="C2132" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2132" t="n">
         <v>100</v>
@@ -49464,7 +49460,7 @@
         </is>
       </c>
       <c r="C2133" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2133" t="n">
         <v>100</v>
@@ -49487,7 +49483,7 @@
         </is>
       </c>
       <c r="C2134" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2134" t="n">
         <v>100</v>
@@ -49510,7 +49506,7 @@
         </is>
       </c>
       <c r="C2135" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2135" t="n">
         <v>100</v>
@@ -49533,7 +49529,7 @@
         </is>
       </c>
       <c r="C2136" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2136" t="n">
         <v>100</v>
@@ -49556,7 +49552,7 @@
         </is>
       </c>
       <c r="C2137" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2137" t="n">
         <v>100</v>
@@ -49579,7 +49575,7 @@
         </is>
       </c>
       <c r="C2138" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2138" t="n">
         <v>100</v>
@@ -49602,7 +49598,7 @@
         </is>
       </c>
       <c r="C2139" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2139" t="n">
         <v>100</v>
@@ -49625,7 +49621,7 @@
         </is>
       </c>
       <c r="C2140" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2140" t="n">
         <v>100</v>
@@ -49648,7 +49644,7 @@
         </is>
       </c>
       <c r="C2141" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2141" t="n">
         <v>100</v>
@@ -49671,7 +49667,7 @@
         </is>
       </c>
       <c r="C2142" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2142" t="n">
         <v>100</v>
@@ -49694,7 +49690,7 @@
         </is>
       </c>
       <c r="C2143" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2143" t="n">
         <v>100</v>
@@ -49717,7 +49713,7 @@
         </is>
       </c>
       <c r="C2144" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2144" t="n">
         <v>100</v>
@@ -49740,7 +49736,7 @@
         </is>
       </c>
       <c r="C2145" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2145" t="n">
         <v>100</v>
@@ -49763,7 +49759,7 @@
         </is>
       </c>
       <c r="C2146" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2146" t="n">
         <v>100</v>
@@ -49786,7 +49782,7 @@
         </is>
       </c>
       <c r="C2147" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2147" t="n">
         <v>100</v>
@@ -49809,7 +49805,7 @@
         </is>
       </c>
       <c r="C2148" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2148" t="n">
         <v>100</v>
@@ -49832,7 +49828,7 @@
         </is>
       </c>
       <c r="C2149" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2149" t="n">
         <v>100</v>
@@ -49855,7 +49851,7 @@
         </is>
       </c>
       <c r="C2150" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2150" t="n">
         <v>100</v>
@@ -49878,7 +49874,7 @@
         </is>
       </c>
       <c r="C2151" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2151" t="n">
         <v>100</v>
@@ -49901,7 +49897,7 @@
         </is>
       </c>
       <c r="C2152" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2152" t="n">
         <v>100</v>
@@ -49924,7 +49920,7 @@
         </is>
       </c>
       <c r="C2153" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2153" t="n">
         <v>100</v>
@@ -49947,7 +49943,7 @@
         </is>
       </c>
       <c r="C2154" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2154" t="n">
         <v>100</v>
@@ -49970,7 +49966,7 @@
         </is>
       </c>
       <c r="C2155" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2155" t="n">
         <v>100</v>
@@ -49993,7 +49989,7 @@
         </is>
       </c>
       <c r="C2156" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2156" t="n">
         <v>100</v>
@@ -50016,7 +50012,7 @@
         </is>
       </c>
       <c r="C2157" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2157" t="n">
         <v>100</v>
@@ -50039,7 +50035,7 @@
         </is>
       </c>
       <c r="C2158" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2158" t="n">
         <v>100</v>
@@ -50062,7 +50058,7 @@
         </is>
       </c>
       <c r="C2159" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2159" t="n">
         <v>100</v>
@@ -50085,7 +50081,7 @@
         </is>
       </c>
       <c r="C2160" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2160" t="n">
         <v>100</v>
@@ -50108,7 +50104,7 @@
         </is>
       </c>
       <c r="C2161" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2161" t="n">
         <v>100</v>
@@ -50131,7 +50127,7 @@
         </is>
       </c>
       <c r="C2162" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2162" t="n">
         <v>100</v>
@@ -50154,7 +50150,7 @@
         </is>
       </c>
       <c r="C2163" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2163" t="n">
         <v>100</v>
@@ -50177,12 +50173,11 @@
         </is>
       </c>
       <c r="C2164" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2164" t="n">
         <v>100</v>
       </c>
-      <c r="E2164" t="inlineStr"/>
     </row>
     <row r="2165">
       <c r="A2165" t="inlineStr">
@@ -50196,12 +50191,11 @@
         </is>
       </c>
       <c r="C2165" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2165" t="n">
         <v>100</v>
       </c>
-      <c r="E2165" t="inlineStr"/>
     </row>
     <row r="2166">
       <c r="A2166" t="inlineStr">
@@ -50215,12 +50209,11 @@
         </is>
       </c>
       <c r="C2166" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2166" t="n">
         <v>100</v>
       </c>
-      <c r="E2166" t="inlineStr"/>
     </row>
     <row r="2167">
       <c r="A2167" t="inlineStr">
@@ -50234,12 +50227,11 @@
         </is>
       </c>
       <c r="C2167" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2167" t="n">
         <v>100</v>
       </c>
-      <c r="E2167" t="inlineStr"/>
     </row>
     <row r="2168">
       <c r="A2168" t="inlineStr">
@@ -50253,12 +50245,11 @@
         </is>
       </c>
       <c r="C2168" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2168" t="n">
         <v>100</v>
       </c>
-      <c r="E2168" t="inlineStr"/>
     </row>
     <row r="2169">
       <c r="A2169" t="inlineStr">
@@ -50272,12 +50263,11 @@
         </is>
       </c>
       <c r="C2169" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2169" t="n">
         <v>100</v>
       </c>
-      <c r="E2169" t="inlineStr"/>
     </row>
     <row r="2170">
       <c r="A2170" t="inlineStr">
@@ -50291,12 +50281,11 @@
         </is>
       </c>
       <c r="C2170" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2170" t="n">
         <v>100</v>
       </c>
-      <c r="E2170" t="inlineStr"/>
     </row>
     <row r="2171">
       <c r="A2171" t="inlineStr">
@@ -50310,12 +50299,11 @@
         </is>
       </c>
       <c r="C2171" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2171" t="n">
         <v>100</v>
       </c>
-      <c r="E2171" t="inlineStr"/>
     </row>
     <row r="2172">
       <c r="A2172" t="inlineStr">
@@ -50329,12 +50317,11 @@
         </is>
       </c>
       <c r="C2172" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2172" t="n">
         <v>100</v>
       </c>
-      <c r="E2172" t="inlineStr"/>
     </row>
     <row r="2173">
       <c r="A2173" t="inlineStr">
@@ -50348,12 +50335,11 @@
         </is>
       </c>
       <c r="C2173" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2173" t="n">
         <v>100</v>
       </c>
-      <c r="E2173" t="inlineStr"/>
     </row>
     <row r="2174">
       <c r="A2174" t="inlineStr">
@@ -50367,12 +50353,11 @@
         </is>
       </c>
       <c r="C2174" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2174" t="n">
         <v>100</v>
       </c>
-      <c r="E2174" t="inlineStr"/>
     </row>
     <row r="2175">
       <c r="A2175" t="inlineStr">
@@ -50386,12 +50371,11 @@
         </is>
       </c>
       <c r="C2175" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2175" t="n">
         <v>100</v>
       </c>
-      <c r="E2175" t="inlineStr"/>
     </row>
     <row r="2176">
       <c r="A2176" t="inlineStr">
@@ -50405,12 +50389,11 @@
         </is>
       </c>
       <c r="C2176" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2176" t="n">
         <v>100</v>
       </c>
-      <c r="E2176" t="inlineStr"/>
     </row>
     <row r="2177">
       <c r="A2177" t="inlineStr">
@@ -50424,12 +50407,11 @@
         </is>
       </c>
       <c r="C2177" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2177" t="n">
         <v>100</v>
       </c>
-      <c r="E2177" t="inlineStr"/>
     </row>
     <row r="2178">
       <c r="A2178" t="inlineStr">
@@ -50443,12 +50425,11 @@
         </is>
       </c>
       <c r="C2178" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2178" t="n">
         <v>100</v>
       </c>
-      <c r="E2178" t="inlineStr"/>
     </row>
     <row r="2179">
       <c r="A2179" t="inlineStr">
@@ -50462,12 +50443,11 @@
         </is>
       </c>
       <c r="C2179" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2179" t="n">
         <v>100</v>
       </c>
-      <c r="E2179" t="inlineStr"/>
     </row>
     <row r="2180">
       <c r="A2180" t="inlineStr">
@@ -50481,12 +50461,11 @@
         </is>
       </c>
       <c r="C2180" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2180" t="n">
         <v>100</v>
       </c>
-      <c r="E2180" t="inlineStr"/>
     </row>
     <row r="2181">
       <c r="A2181" t="inlineStr">
@@ -50500,12 +50479,11 @@
         </is>
       </c>
       <c r="C2181" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2181" t="n">
         <v>100</v>
       </c>
-      <c r="E2181" t="inlineStr"/>
     </row>
     <row r="2182">
       <c r="A2182" t="inlineStr">
@@ -50519,7 +50497,7 @@
         </is>
       </c>
       <c r="C2182" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2182" t="n">
         <v>100</v>
@@ -50542,7 +50520,7 @@
         </is>
       </c>
       <c r="C2183" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2183" t="n">
         <v>100</v>
@@ -50565,7 +50543,7 @@
         </is>
       </c>
       <c r="C2184" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2184" t="n">
         <v>100</v>
@@ -50588,7 +50566,7 @@
         </is>
       </c>
       <c r="C2185" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2185" t="n">
         <v>100</v>
@@ -50611,7 +50589,7 @@
         </is>
       </c>
       <c r="C2186" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2186" t="n">
         <v>100</v>
@@ -50634,7 +50612,7 @@
         </is>
       </c>
       <c r="C2187" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2187" t="n">
         <v>100</v>
@@ -50657,7 +50635,7 @@
         </is>
       </c>
       <c r="C2188" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2188" t="n">
         <v>100</v>
@@ -50680,7 +50658,7 @@
         </is>
       </c>
       <c r="C2189" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2189" t="n">
         <v>100</v>
@@ -50703,7 +50681,7 @@
         </is>
       </c>
       <c r="C2190" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2190" t="n">
         <v>100</v>
@@ -50726,7 +50704,7 @@
         </is>
       </c>
       <c r="C2191" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2191" t="n">
         <v>100</v>
@@ -50749,7 +50727,7 @@
         </is>
       </c>
       <c r="C2192" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2192" t="n">
         <v>100</v>
@@ -50772,7 +50750,7 @@
         </is>
       </c>
       <c r="C2193" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2193" t="n">
         <v>100</v>
@@ -50795,7 +50773,7 @@
         </is>
       </c>
       <c r="C2194" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2194" t="n">
         <v>100</v>
@@ -50818,7 +50796,7 @@
         </is>
       </c>
       <c r="C2195" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2195" t="n">
         <v>100</v>
@@ -50841,7 +50819,7 @@
         </is>
       </c>
       <c r="C2196" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2196" t="n">
         <v>100</v>
@@ -50864,7 +50842,7 @@
         </is>
       </c>
       <c r="C2197" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2197" t="n">
         <v>100</v>
@@ -50887,7 +50865,7 @@
         </is>
       </c>
       <c r="C2198" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2198" t="n">
         <v>100</v>
@@ -50910,7 +50888,7 @@
         </is>
       </c>
       <c r="C2199" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2199" t="n">
         <v>100</v>
@@ -50933,7 +50911,7 @@
         </is>
       </c>
       <c r="C2200" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2200" t="n">
         <v>100</v>
@@ -50956,7 +50934,7 @@
         </is>
       </c>
       <c r="C2201" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2201" t="n">
         <v>100</v>
@@ -50979,7 +50957,7 @@
         </is>
       </c>
       <c r="C2202" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2202" t="n">
         <v>100</v>
@@ -51002,7 +50980,7 @@
         </is>
       </c>
       <c r="C2203" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2203" t="n">
         <v>100</v>
@@ -51025,7 +51003,7 @@
         </is>
       </c>
       <c r="C2204" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2204" t="n">
         <v>100</v>
@@ -51048,7 +51026,7 @@
         </is>
       </c>
       <c r="C2205" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2205" t="n">
         <v>100</v>
@@ -51071,7 +51049,7 @@
         </is>
       </c>
       <c r="C2206" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2206" t="n">
         <v>100</v>
@@ -51094,7 +51072,7 @@
         </is>
       </c>
       <c r="C2207" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2207" t="n">
         <v>100</v>
@@ -51117,7 +51095,7 @@
         </is>
       </c>
       <c r="C2208" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2208" t="n">
         <v>100</v>
@@ -51140,7 +51118,7 @@
         </is>
       </c>
       <c r="C2209" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2209" t="n">
         <v>100</v>
@@ -51163,7 +51141,7 @@
         </is>
       </c>
       <c r="C2210" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2210" t="n">
         <v>100</v>
@@ -51186,7 +51164,7 @@
         </is>
       </c>
       <c r="C2211" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2211" t="n">
         <v>100</v>
@@ -51209,7 +51187,7 @@
         </is>
       </c>
       <c r="C2212" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2212" t="n">
         <v>100</v>
@@ -51232,7 +51210,7 @@
         </is>
       </c>
       <c r="C2213" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2213" t="n">
         <v>100</v>
@@ -51669,7 +51647,7 @@
         </is>
       </c>
       <c r="C2232" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2232" t="n">
         <v>100</v>
@@ -51692,7 +51670,7 @@
         </is>
       </c>
       <c r="C2233" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2233" t="n">
         <v>100</v>
@@ -51715,7 +51693,7 @@
         </is>
       </c>
       <c r="C2234" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2234" t="n">
         <v>100</v>
@@ -51738,7 +51716,7 @@
         </is>
       </c>
       <c r="C2235" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2235" t="n">
         <v>100</v>
@@ -51761,7 +51739,7 @@
         </is>
       </c>
       <c r="C2236" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2236" t="n">
         <v>100</v>
@@ -51784,7 +51762,7 @@
         </is>
       </c>
       <c r="C2237" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2237" t="n">
         <v>100</v>
@@ -51807,7 +51785,7 @@
         </is>
       </c>
       <c r="C2238" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2238" t="n">
         <v>100</v>
@@ -51830,7 +51808,7 @@
         </is>
       </c>
       <c r="C2239" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2239" t="n">
         <v>100</v>
@@ -51853,7 +51831,7 @@
         </is>
       </c>
       <c r="C2240" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2240" t="n">
         <v>100</v>
@@ -51876,7 +51854,7 @@
         </is>
       </c>
       <c r="C2241" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2241" t="n">
         <v>100</v>
@@ -51899,7 +51877,7 @@
         </is>
       </c>
       <c r="C2242" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2242" t="n">
         <v>100</v>
@@ -51922,7 +51900,7 @@
         </is>
       </c>
       <c r="C2243" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2243" t="n">
         <v>100</v>
@@ -51945,7 +51923,7 @@
         </is>
       </c>
       <c r="C2244" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2244" t="n">
         <v>100</v>
@@ -51968,7 +51946,7 @@
         </is>
       </c>
       <c r="C2245" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2245" t="n">
         <v>100</v>
@@ -51991,7 +51969,7 @@
         </is>
       </c>
       <c r="C2246" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2246" t="n">
         <v>100</v>
@@ -52014,7 +51992,7 @@
         </is>
       </c>
       <c r="C2247" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2247" t="n">
         <v>100</v>
@@ -52037,7 +52015,7 @@
         </is>
       </c>
       <c r="C2248" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2248" t="n">
         <v>100</v>
@@ -52060,7 +52038,7 @@
         </is>
       </c>
       <c r="C2249" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2249" t="n">
         <v>100</v>
@@ -52083,7 +52061,7 @@
         </is>
       </c>
       <c r="C2250" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2250" t="n">
         <v>100</v>
@@ -52106,7 +52084,7 @@
         </is>
       </c>
       <c r="C2251" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2251" t="n">
         <v>100</v>
@@ -52129,7 +52107,7 @@
         </is>
       </c>
       <c r="C2252" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2252" t="n">
         <v>100</v>
@@ -52152,7 +52130,7 @@
         </is>
       </c>
       <c r="C2253" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2253" t="n">
         <v>100</v>
@@ -52175,7 +52153,7 @@
         </is>
       </c>
       <c r="C2254" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2254" t="n">
         <v>100</v>
@@ -52198,7 +52176,7 @@
         </is>
       </c>
       <c r="C2255" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2255" t="n">
         <v>100</v>
@@ -52221,7 +52199,7 @@
         </is>
       </c>
       <c r="C2256" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2256" t="n">
         <v>100</v>
@@ -52244,7 +52222,7 @@
         </is>
       </c>
       <c r="C2257" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2257" t="n">
         <v>100</v>
@@ -52267,7 +52245,7 @@
         </is>
       </c>
       <c r="C2258" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2258" t="n">
         <v>100</v>
@@ -52290,7 +52268,7 @@
         </is>
       </c>
       <c r="C2259" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2259" t="n">
         <v>100</v>
@@ -52313,7 +52291,7 @@
         </is>
       </c>
       <c r="C2260" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2260" t="n">
         <v>100</v>
@@ -52336,7 +52314,7 @@
         </is>
       </c>
       <c r="C2261" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2261" t="n">
         <v>100</v>
@@ -52359,7 +52337,7 @@
         </is>
       </c>
       <c r="C2262" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2262" t="n">
         <v>100</v>
@@ -52382,7 +52360,7 @@
         </is>
       </c>
       <c r="C2263" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2263" t="n">
         <v>100</v>
@@ -52405,12 +52383,11 @@
         </is>
       </c>
       <c r="C2264" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2264" t="n">
         <v>100</v>
       </c>
-      <c r="E2264" t="inlineStr"/>
     </row>
     <row r="2265">
       <c r="A2265" t="inlineStr">
@@ -52424,12 +52401,11 @@
         </is>
       </c>
       <c r="C2265" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2265" t="n">
         <v>100</v>
       </c>
-      <c r="E2265" t="inlineStr"/>
     </row>
     <row r="2266">
       <c r="A2266" t="inlineStr">
@@ -52443,7 +52419,7 @@
         </is>
       </c>
       <c r="C2266" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2266" t="n">
         <v>100</v>
@@ -52466,12 +52442,11 @@
         </is>
       </c>
       <c r="C2267" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2267" t="n">
         <v>100</v>
       </c>
-      <c r="E2267" t="inlineStr"/>
     </row>
     <row r="2268">
       <c r="A2268" t="inlineStr">
@@ -52485,7 +52460,7 @@
         </is>
       </c>
       <c r="C2268" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2268" t="n">
         <v>100</v>
@@ -52508,7 +52483,7 @@
         </is>
       </c>
       <c r="C2269" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2269" t="n">
         <v>100</v>
@@ -52531,7 +52506,7 @@
         </is>
       </c>
       <c r="C2270" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2270" t="n">
         <v>100</v>
@@ -52554,7 +52529,7 @@
         </is>
       </c>
       <c r="C2271" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2271" t="n">
         <v>100</v>
@@ -52577,7 +52552,7 @@
         </is>
       </c>
       <c r="C2272" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2272" t="n">
         <v>100</v>
@@ -52600,7 +52575,7 @@
         </is>
       </c>
       <c r="C2273" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2273" t="n">
         <v>100</v>
@@ -52623,7 +52598,7 @@
         </is>
       </c>
       <c r="C2274" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2274" t="n">
         <v>100</v>
@@ -52646,7 +52621,7 @@
         </is>
       </c>
       <c r="C2275" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2275" t="n">
         <v>100</v>
@@ -52669,7 +52644,7 @@
         </is>
       </c>
       <c r="C2276" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2276" t="n">
         <v>100</v>
@@ -52692,7 +52667,7 @@
         </is>
       </c>
       <c r="C2277" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2277" t="n">
         <v>100</v>
@@ -52715,7 +52690,7 @@
         </is>
       </c>
       <c r="C2278" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2278" t="n">
         <v>100</v>
@@ -52738,7 +52713,7 @@
         </is>
       </c>
       <c r="C2279" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2279" t="n">
         <v>100</v>
@@ -52761,7 +52736,7 @@
         </is>
       </c>
       <c r="C2280" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2280" t="n">
         <v>100</v>
@@ -52784,7 +52759,7 @@
         </is>
       </c>
       <c r="C2281" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2281" t="n">
         <v>100</v>
@@ -52807,7 +52782,7 @@
         </is>
       </c>
       <c r="C2282" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2282" t="n">
         <v>100</v>
@@ -52830,7 +52805,7 @@
         </is>
       </c>
       <c r="C2283" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2283" t="n">
         <v>100</v>
@@ -52853,7 +52828,7 @@
         </is>
       </c>
       <c r="C2284" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2284" t="n">
         <v>100</v>
@@ -52876,7 +52851,7 @@
         </is>
       </c>
       <c r="C2285" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2285" t="n">
         <v>100</v>
@@ -52899,7 +52874,7 @@
         </is>
       </c>
       <c r="C2286" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2286" t="n">
         <v>100</v>
@@ -52922,7 +52897,7 @@
         </is>
       </c>
       <c r="C2287" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2287" t="n">
         <v>100</v>
@@ -52945,7 +52920,7 @@
         </is>
       </c>
       <c r="C2288" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2288" t="n">
         <v>100</v>
@@ -52968,7 +52943,7 @@
         </is>
       </c>
       <c r="C2289" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2289" t="n">
         <v>100</v>
@@ -52991,7 +52966,7 @@
         </is>
       </c>
       <c r="C2290" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2290" t="n">
         <v>100</v>
@@ -53014,7 +52989,7 @@
         </is>
       </c>
       <c r="C2291" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2291" t="n">
         <v>100</v>
@@ -53037,7 +53012,7 @@
         </is>
       </c>
       <c r="C2292" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2292" t="n">
         <v>100</v>
@@ -53060,7 +53035,7 @@
         </is>
       </c>
       <c r="C2293" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2293" t="n">
         <v>100</v>
@@ -53083,7 +53058,7 @@
         </is>
       </c>
       <c r="C2294" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2294" t="n">
         <v>100</v>
@@ -53106,7 +53081,7 @@
         </is>
       </c>
       <c r="C2295" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2295" t="n">
         <v>100</v>
@@ -53129,7 +53104,7 @@
         </is>
       </c>
       <c r="C2296" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2296" t="n">
         <v>100</v>
@@ -53152,7 +53127,7 @@
         </is>
       </c>
       <c r="C2297" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2297" t="n">
         <v>100</v>
@@ -53175,7 +53150,7 @@
         </is>
       </c>
       <c r="C2298" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2298" t="n">
         <v>100</v>
@@ -53198,7 +53173,7 @@
         </is>
       </c>
       <c r="C2299" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2299" t="n">
         <v>100</v>
@@ -53221,7 +53196,7 @@
         </is>
       </c>
       <c r="C2300" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2300" t="n">
         <v>100</v>
@@ -53244,7 +53219,7 @@
         </is>
       </c>
       <c r="C2301" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2301" t="n">
         <v>100</v>
@@ -53267,7 +53242,7 @@
         </is>
       </c>
       <c r="C2302" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2302" t="n">
         <v>100</v>
@@ -53290,7 +53265,7 @@
         </is>
       </c>
       <c r="C2303" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2303" t="n">
         <v>100</v>
@@ -53313,7 +53288,7 @@
         </is>
       </c>
       <c r="C2304" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2304" t="n">
         <v>100</v>
@@ -53336,7 +53311,7 @@
         </is>
       </c>
       <c r="C2305" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2305" t="n">
         <v>100</v>
@@ -53359,7 +53334,7 @@
         </is>
       </c>
       <c r="C2306" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2306" t="n">
         <v>100</v>
@@ -53382,7 +53357,7 @@
         </is>
       </c>
       <c r="C2307" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2307" t="n">
         <v>100</v>
@@ -53405,7 +53380,7 @@
         </is>
       </c>
       <c r="C2308" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2308" t="n">
         <v>100</v>
@@ -53428,7 +53403,7 @@
         </is>
       </c>
       <c r="C2309" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2309" t="n">
         <v>100</v>
@@ -53451,7 +53426,7 @@
         </is>
       </c>
       <c r="C2310" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2310" t="n">
         <v>100</v>
@@ -53474,7 +53449,7 @@
         </is>
       </c>
       <c r="C2311" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2311" t="n">
         <v>100</v>
@@ -53497,7 +53472,7 @@
         </is>
       </c>
       <c r="C2312" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2312" t="n">
         <v>100</v>
@@ -53520,7 +53495,7 @@
         </is>
       </c>
       <c r="C2313" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2313" t="n">
         <v>100</v>
@@ -53543,7 +53518,7 @@
         </is>
       </c>
       <c r="C2314" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2314" t="n">
         <v>100</v>
@@ -53566,7 +53541,7 @@
         </is>
       </c>
       <c r="C2315" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2315" t="n">
         <v>100</v>
@@ -53589,7 +53564,7 @@
         </is>
       </c>
       <c r="C2316" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2316" t="n">
         <v>100</v>
@@ -53612,7 +53587,7 @@
         </is>
       </c>
       <c r="C2317" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2317" t="n">
         <v>100</v>
@@ -53635,7 +53610,7 @@
         </is>
       </c>
       <c r="C2318" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2318" t="n">
         <v>100</v>
@@ -53658,7 +53633,7 @@
         </is>
       </c>
       <c r="C2319" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2319" t="n">
         <v>100</v>
@@ -53681,7 +53656,7 @@
         </is>
       </c>
       <c r="C2320" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2320" t="n">
         <v>100</v>
@@ -53704,7 +53679,7 @@
         </is>
       </c>
       <c r="C2321" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2321" t="n">
         <v>100</v>
@@ -53727,7 +53702,7 @@
         </is>
       </c>
       <c r="C2322" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2322" t="n">
         <v>100</v>
@@ -53750,7 +53725,7 @@
         </is>
       </c>
       <c r="C2323" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2323" t="n">
         <v>100</v>
@@ -53773,7 +53748,7 @@
         </is>
       </c>
       <c r="C2324" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2324" t="n">
         <v>100</v>
@@ -53796,7 +53771,7 @@
         </is>
       </c>
       <c r="C2325" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2325" t="n">
         <v>100</v>
@@ -53819,7 +53794,7 @@
         </is>
       </c>
       <c r="C2326" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2326" t="n">
         <v>100</v>
@@ -53842,7 +53817,7 @@
         </is>
       </c>
       <c r="C2327" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2327" t="n">
         <v>100</v>
@@ -53865,7 +53840,7 @@
         </is>
       </c>
       <c r="C2328" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2328" t="n">
         <v>100</v>
@@ -53888,7 +53863,7 @@
         </is>
       </c>
       <c r="C2329" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2329" t="n">
         <v>100</v>
@@ -53911,7 +53886,7 @@
         </is>
       </c>
       <c r="C2330" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2330" t="n">
         <v>100</v>
@@ -53934,7 +53909,7 @@
         </is>
       </c>
       <c r="C2331" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2331" t="n">
         <v>100</v>
@@ -53957,7 +53932,7 @@
         </is>
       </c>
       <c r="C2332" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2332" t="n">
         <v>100</v>
@@ -53980,7 +53955,7 @@
         </is>
       </c>
       <c r="C2333" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2333" t="n">
         <v>100</v>
@@ -54003,7 +53978,7 @@
         </is>
       </c>
       <c r="C2334" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2334" t="n">
         <v>100</v>
@@ -54026,7 +54001,7 @@
         </is>
       </c>
       <c r="C2335" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2335" t="n">
         <v>100</v>
@@ -54049,7 +54024,7 @@
         </is>
       </c>
       <c r="C2336" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2336" t="n">
         <v>100</v>
@@ -54066,9 +54041,8 @@
           <t>15N2951OY</t>
         </is>
       </c>
-      <c r="B2337" t="inlineStr"/>
       <c r="C2337" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2337" t="n">
         <v>100</v>
@@ -54085,9 +54059,8 @@
           <t>15N2951Z</t>
         </is>
       </c>
-      <c r="B2338" t="inlineStr"/>
       <c r="C2338" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2338" t="n">
         <v>100</v>
@@ -54110,7 +54083,7 @@
         </is>
       </c>
       <c r="C2339" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2339" t="n">
         <v>100</v>
@@ -54133,7 +54106,7 @@
         </is>
       </c>
       <c r="C2340" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2340" t="n">
         <v>100</v>
@@ -54156,7 +54129,7 @@
         </is>
       </c>
       <c r="C2341" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2341" t="n">
         <v>100</v>
@@ -54179,7 +54152,7 @@
         </is>
       </c>
       <c r="C2342" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2342" t="n">
         <v>100</v>
@@ -54202,7 +54175,7 @@
         </is>
       </c>
       <c r="C2343" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2343" t="n">
         <v>100</v>
@@ -54225,7 +54198,7 @@
         </is>
       </c>
       <c r="C2344" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2344" t="n">
         <v>100</v>
@@ -54248,7 +54221,7 @@
         </is>
       </c>
       <c r="C2345" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2345" t="n">
         <v>100</v>
@@ -54271,7 +54244,7 @@
         </is>
       </c>
       <c r="C2346" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2346" t="n">
         <v>100</v>
@@ -54294,7 +54267,7 @@
         </is>
       </c>
       <c r="C2347" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2347" t="n">
         <v>100</v>
@@ -54317,7 +54290,7 @@
         </is>
       </c>
       <c r="C2348" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2348" t="n">
         <v>100</v>
@@ -54340,7 +54313,7 @@
         </is>
       </c>
       <c r="C2349" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2349" t="n">
         <v>100</v>
@@ -54363,7 +54336,7 @@
         </is>
       </c>
       <c r="C2350" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2350" t="n">
         <v>100</v>
@@ -54386,7 +54359,7 @@
         </is>
       </c>
       <c r="C2351" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2351" t="n">
         <v>100</v>
@@ -54409,7 +54382,7 @@
         </is>
       </c>
       <c r="C2352" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2352" t="n">
         <v>100</v>
@@ -54432,7 +54405,7 @@
         </is>
       </c>
       <c r="C2353" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2353" t="n">
         <v>100</v>
@@ -54455,7 +54428,7 @@
         </is>
       </c>
       <c r="C2354" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2354" t="n">
         <v>100</v>
@@ -54478,7 +54451,7 @@
         </is>
       </c>
       <c r="C2355" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2355" t="n">
         <v>100</v>
@@ -54501,7 +54474,7 @@
         </is>
       </c>
       <c r="C2356" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2356" t="n">
         <v>100</v>
@@ -54524,7 +54497,7 @@
         </is>
       </c>
       <c r="C2357" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2357" t="n">
         <v>100</v>
@@ -54547,7 +54520,7 @@
         </is>
       </c>
       <c r="C2358" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2358" t="n">
         <v>100</v>
@@ -54570,7 +54543,7 @@
         </is>
       </c>
       <c r="C2359" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2359" t="n">
         <v>100</v>
@@ -54593,7 +54566,7 @@
         </is>
       </c>
       <c r="C2360" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2360" t="n">
         <v>100</v>
@@ -54616,7 +54589,7 @@
         </is>
       </c>
       <c r="C2361" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2361" t="n">
         <v>100</v>
@@ -54639,7 +54612,7 @@
         </is>
       </c>
       <c r="C2362" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2362" t="n">
         <v>100</v>
@@ -54662,7 +54635,7 @@
         </is>
       </c>
       <c r="C2363" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2363" t="n">
         <v>100</v>
@@ -54685,7 +54658,7 @@
         </is>
       </c>
       <c r="C2364" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2364" t="n">
         <v>100</v>
@@ -54708,7 +54681,7 @@
         </is>
       </c>
       <c r="C2365" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2365" t="n">
         <v>100</v>
@@ -54731,7 +54704,7 @@
         </is>
       </c>
       <c r="C2366" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2366" t="n">
         <v>100</v>
@@ -54754,7 +54727,7 @@
         </is>
       </c>
       <c r="C2367" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2367" t="n">
         <v>100</v>
@@ -54777,7 +54750,7 @@
         </is>
       </c>
       <c r="C2368" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2368" t="n">
         <v>100</v>
@@ -54800,7 +54773,7 @@
         </is>
       </c>
       <c r="C2369" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2369" t="n">
         <v>100</v>
@@ -54823,7 +54796,7 @@
         </is>
       </c>
       <c r="C2370" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2370" t="n">
         <v>100</v>
@@ -54846,7 +54819,7 @@
         </is>
       </c>
       <c r="C2371" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2371" t="n">
         <v>100</v>
@@ -54869,7 +54842,7 @@
         </is>
       </c>
       <c r="C2372" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2372" t="n">
         <v>100</v>
@@ -54892,7 +54865,7 @@
         </is>
       </c>
       <c r="C2373" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2373" t="n">
         <v>100</v>
@@ -54915,7 +54888,7 @@
         </is>
       </c>
       <c r="C2374" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2374" t="n">
         <v>100</v>
@@ -54938,7 +54911,7 @@
         </is>
       </c>
       <c r="C2375" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2375" t="n">
         <v>100</v>
@@ -54955,9 +54928,8 @@
           <t>15N580801OJ</t>
         </is>
       </c>
-      <c r="B2376" t="inlineStr"/>
       <c r="C2376" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2376" t="n">
         <v>100</v>
@@ -54974,9 +54946,8 @@
           <t>15N580801OY</t>
         </is>
       </c>
-      <c r="B2377" t="inlineStr"/>
       <c r="C2377" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2377" t="n">
         <v>100</v>
@@ -54999,7 +54970,7 @@
         </is>
       </c>
       <c r="C2378" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2378" t="n">
         <v>100</v>
@@ -55022,7 +54993,7 @@
         </is>
       </c>
       <c r="C2379" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2379" t="n">
         <v>100</v>
@@ -55045,7 +55016,7 @@
         </is>
       </c>
       <c r="C2380" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2380" t="n">
         <v>100</v>
@@ -55068,7 +55039,7 @@
         </is>
       </c>
       <c r="C2381" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2381" t="n">
         <v>100</v>
@@ -55091,7 +55062,7 @@
         </is>
       </c>
       <c r="C2382" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2382" t="n">
         <v>100</v>
@@ -55108,9 +55079,8 @@
           <t>15N5820TJ</t>
         </is>
       </c>
-      <c r="B2383" t="inlineStr"/>
       <c r="C2383" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2383" t="n">
         <v>100</v>
@@ -55127,9 +55097,8 @@
           <t>15N5820TY</t>
         </is>
       </c>
-      <c r="B2384" t="inlineStr"/>
       <c r="C2384" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2384" t="n">
         <v>100</v>
@@ -55152,7 +55121,7 @@
         </is>
       </c>
       <c r="C2385" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2385" t="n">
         <v>100</v>
@@ -55175,7 +55144,7 @@
         </is>
       </c>
       <c r="C2386" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2386" t="n">
         <v>100</v>
@@ -55198,7 +55167,7 @@
         </is>
       </c>
       <c r="C2387" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2387" t="n">
         <v>100</v>
@@ -55221,7 +55190,7 @@
         </is>
       </c>
       <c r="C2388" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2388" t="n">
         <v>100</v>
@@ -55244,7 +55213,7 @@
         </is>
       </c>
       <c r="C2389" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2389" t="n">
         <v>100</v>
@@ -55267,7 +55236,7 @@
         </is>
       </c>
       <c r="C2390" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2390" t="n">
         <v>100</v>
@@ -55290,7 +55259,7 @@
         </is>
       </c>
       <c r="C2391" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2391" t="n">
         <v>100</v>
@@ -55313,7 +55282,7 @@
         </is>
       </c>
       <c r="C2392" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2392" t="n">
         <v>100</v>
@@ -55336,7 +55305,7 @@
         </is>
       </c>
       <c r="C2393" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2393" t="n">
         <v>12</v>
@@ -55359,7 +55328,7 @@
         </is>
       </c>
       <c r="C2394" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2394" t="n">
         <v>12</v>
@@ -55382,7 +55351,7 @@
         </is>
       </c>
       <c r="C2395" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2395" t="n">
         <v>12</v>
@@ -55405,7 +55374,7 @@
         </is>
       </c>
       <c r="C2396" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2396" t="n">
         <v>30</v>
@@ -55428,7 +55397,7 @@
         </is>
       </c>
       <c r="C2397" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2397" t="n">
         <v>12</v>
@@ -55451,7 +55420,7 @@
         </is>
       </c>
       <c r="C2398" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2398" t="n">
         <v>12</v>
@@ -55474,7 +55443,7 @@
         </is>
       </c>
       <c r="C2399" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2399" t="n">
         <v>12</v>
@@ -55497,7 +55466,7 @@
         </is>
       </c>
       <c r="C2400" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2400" t="n">
         <v>12</v>
@@ -55520,7 +55489,7 @@
         </is>
       </c>
       <c r="C2401" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2401" t="n">
         <v>12</v>
@@ -55543,7 +55512,7 @@
         </is>
       </c>
       <c r="C2402" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2402" t="n">
         <v>12</v>
@@ -55566,7 +55535,7 @@
         </is>
       </c>
       <c r="C2403" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2403" t="n">
         <v>12</v>
@@ -55589,7 +55558,7 @@
         </is>
       </c>
       <c r="C2404" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2404" t="n">
         <v>12</v>
@@ -55612,7 +55581,7 @@
         </is>
       </c>
       <c r="C2405" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2405" t="n">
         <v>12</v>
@@ -55635,7 +55604,7 @@
         </is>
       </c>
       <c r="C2406" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2406" t="n">
         <v>12</v>
@@ -55658,7 +55627,7 @@
         </is>
       </c>
       <c r="C2407" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2407" t="n">
         <v>12</v>
@@ -55681,7 +55650,7 @@
         </is>
       </c>
       <c r="C2408" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2408" t="n">
         <v>12</v>
@@ -55704,7 +55673,7 @@
         </is>
       </c>
       <c r="C2409" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2409" t="n">
         <v>6</v>
@@ -55727,7 +55696,7 @@
         </is>
       </c>
       <c r="C2410" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2410" t="n">
         <v>12</v>
@@ -55750,7 +55719,7 @@
         </is>
       </c>
       <c r="C2411" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2411" t="n">
         <v>12</v>
@@ -55773,7 +55742,7 @@
         </is>
       </c>
       <c r="C2412" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2412" t="n">
         <v>12</v>
@@ -55796,7 +55765,7 @@
         </is>
       </c>
       <c r="C2413" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2413" t="n">
         <v>12</v>
@@ -55819,7 +55788,7 @@
         </is>
       </c>
       <c r="C2414" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2414" t="n">
         <v>12</v>
@@ -55842,7 +55811,7 @@
         </is>
       </c>
       <c r="C2415" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2415" t="n">
         <v>12</v>
@@ -55865,7 +55834,7 @@
         </is>
       </c>
       <c r="C2416" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2416" t="n">
         <v>12</v>
@@ -55888,7 +55857,7 @@
         </is>
       </c>
       <c r="C2417" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2417" t="n">
         <v>12</v>
@@ -55911,7 +55880,7 @@
         </is>
       </c>
       <c r="C2418" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2418" t="n">
         <v>4</v>
@@ -55934,7 +55903,7 @@
         </is>
       </c>
       <c r="C2419" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2419" t="n">
         <v>6</v>
@@ -55957,7 +55926,7 @@
         </is>
       </c>
       <c r="C2420" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2420" t="n">
         <v>12</v>
@@ -55980,7 +55949,7 @@
         </is>
       </c>
       <c r="C2421" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2421" t="n">
         <v>12</v>
@@ -56003,7 +55972,7 @@
         </is>
       </c>
       <c r="C2422" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2422" t="n">
         <v>12</v>
@@ -56026,7 +55995,7 @@
         </is>
       </c>
       <c r="C2423" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2423" t="n">
         <v>12</v>
@@ -56049,7 +56018,7 @@
         </is>
       </c>
       <c r="C2424" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2424" t="n">
         <v>12</v>
@@ -56072,7 +56041,7 @@
         </is>
       </c>
       <c r="C2425" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2425" t="n">
         <v>12</v>
@@ -56095,7 +56064,7 @@
         </is>
       </c>
       <c r="C2426" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2426" t="n">
         <v>12</v>
@@ -56118,7 +56087,7 @@
         </is>
       </c>
       <c r="C2427" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2427" t="n">
         <v>12</v>
@@ -56141,7 +56110,7 @@
         </is>
       </c>
       <c r="C2428" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2428" t="n">
         <v>12</v>
@@ -56164,7 +56133,7 @@
         </is>
       </c>
       <c r="C2429" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2429" t="n">
         <v>12</v>
@@ -56187,7 +56156,7 @@
         </is>
       </c>
       <c r="C2430" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2430" t="n">
         <v>12</v>
@@ -56210,7 +56179,7 @@
         </is>
       </c>
       <c r="C2431" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2431" t="n">
         <v>12</v>
@@ -56233,7 +56202,7 @@
         </is>
       </c>
       <c r="C2432" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2432" t="n">
         <v>12</v>
@@ -56256,7 +56225,7 @@
         </is>
       </c>
       <c r="C2433" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2433" t="n">
         <v>12</v>
@@ -56279,7 +56248,7 @@
         </is>
       </c>
       <c r="C2434" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2434" t="n">
         <v>12</v>
@@ -56302,7 +56271,7 @@
         </is>
       </c>
       <c r="C2435" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2435" t="n">
         <v>12</v>
@@ -56325,7 +56294,7 @@
         </is>
       </c>
       <c r="C2436" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2436" t="n">
         <v>12</v>
@@ -56348,7 +56317,7 @@
         </is>
       </c>
       <c r="C2437" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2437" t="n">
         <v>12</v>
@@ -56371,7 +56340,7 @@
         </is>
       </c>
       <c r="C2438" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2438" t="n">
         <v>12</v>
@@ -56394,7 +56363,7 @@
         </is>
       </c>
       <c r="C2439" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2439" t="n">
         <v>27</v>
@@ -56417,7 +56386,7 @@
         </is>
       </c>
       <c r="C2440" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2440" t="n">
         <v>27</v>
@@ -56440,7 +56409,7 @@
         </is>
       </c>
       <c r="C2441" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2441" t="n">
         <v>30</v>
@@ -56463,7 +56432,7 @@
         </is>
       </c>
       <c r="C2442" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2442" t="n">
         <v>27</v>
@@ -56486,7 +56455,7 @@
         </is>
       </c>
       <c r="C2443" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2443" t="n">
         <v>12</v>
@@ -56509,7 +56478,7 @@
         </is>
       </c>
       <c r="C2444" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2444" t="n">
         <v>12</v>
@@ -56532,7 +56501,7 @@
         </is>
       </c>
       <c r="C2445" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2445" t="n">
         <v>16</v>
@@ -56555,7 +56524,7 @@
         </is>
       </c>
       <c r="C2446" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2446" t="n">
         <v>12</v>
@@ -56578,7 +56547,7 @@
         </is>
       </c>
       <c r="C2447" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2447" t="n">
         <v>12</v>
@@ -56601,7 +56570,7 @@
         </is>
       </c>
       <c r="C2448" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2448" t="n">
         <v>20</v>
@@ -56624,7 +56593,7 @@
         </is>
       </c>
       <c r="C2449" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2449" t="n">
         <v>24</v>
@@ -56647,7 +56616,7 @@
         </is>
       </c>
       <c r="C2450" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2450" t="n">
         <v>30</v>
@@ -56670,7 +56639,7 @@
         </is>
       </c>
       <c r="C2451" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2451" t="n">
         <v>30</v>
@@ -56693,7 +56662,7 @@
         </is>
       </c>
       <c r="C2452" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2452" t="n">
         <v>24</v>
@@ -56716,7 +56685,7 @@
         </is>
       </c>
       <c r="C2453" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2453" t="n">
         <v>30</v>
@@ -56739,7 +56708,7 @@
         </is>
       </c>
       <c r="C2454" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2454" t="n">
         <v>30</v>
@@ -56762,7 +56731,7 @@
         </is>
       </c>
       <c r="C2455" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2455" t="n">
         <v>24</v>
@@ -56785,7 +56754,7 @@
         </is>
       </c>
       <c r="C2456" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2456" t="n">
         <v>30</v>
@@ -56808,7 +56777,7 @@
         </is>
       </c>
       <c r="C2457" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2457" t="n">
         <v>30</v>
@@ -56831,7 +56800,7 @@
         </is>
       </c>
       <c r="C2458" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2458" t="n">
         <v>30</v>
@@ -56854,7 +56823,7 @@
         </is>
       </c>
       <c r="C2459" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2459" t="n">
         <v>24</v>
@@ -56877,7 +56846,7 @@
         </is>
       </c>
       <c r="C2460" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2460" t="n">
         <v>30</v>
@@ -56900,7 +56869,7 @@
         </is>
       </c>
       <c r="C2461" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2461" t="n">
         <v>24</v>
@@ -56923,7 +56892,7 @@
         </is>
       </c>
       <c r="C2462" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2462" t="n">
         <v>30</v>
@@ -56946,7 +56915,7 @@
         </is>
       </c>
       <c r="C2463" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2463" t="n">
         <v>6</v>
@@ -56969,7 +56938,7 @@
         </is>
       </c>
       <c r="C2464" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2464" t="n">
         <v>16</v>
@@ -56992,7 +56961,7 @@
         </is>
       </c>
       <c r="C2465" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2465" t="n">
         <v>16</v>
@@ -57015,7 +56984,7 @@
         </is>
       </c>
       <c r="C2466" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2466" t="n">
         <v>16</v>
@@ -57038,7 +57007,7 @@
         </is>
       </c>
       <c r="C2467" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2467" t="n">
         <v>6</v>
@@ -57061,7 +57030,7 @@
         </is>
       </c>
       <c r="C2468" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2468" t="n">
         <v>30</v>
@@ -57084,7 +57053,7 @@
         </is>
       </c>
       <c r="C2469" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2469" t="n">
         <v>12</v>
@@ -57107,7 +57076,7 @@
         </is>
       </c>
       <c r="C2470" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2470" t="n">
         <v>12</v>
@@ -57130,7 +57099,7 @@
         </is>
       </c>
       <c r="C2471" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2471" t="n">
         <v>30</v>
@@ -57153,7 +57122,7 @@
         </is>
       </c>
       <c r="C2472" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2472" t="n">
         <v>30</v>
@@ -57176,7 +57145,7 @@
         </is>
       </c>
       <c r="C2473" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2473" t="n">
         <v>6</v>
@@ -57199,7 +57168,7 @@
         </is>
       </c>
       <c r="C2474" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2474" t="n">
         <v>4</v>
@@ -57222,7 +57191,7 @@
         </is>
       </c>
       <c r="C2475" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2475" t="n">
         <v>12</v>
@@ -57245,7 +57214,7 @@
         </is>
       </c>
       <c r="C2476" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2476" t="n">
         <v>12</v>
@@ -57268,7 +57237,7 @@
         </is>
       </c>
       <c r="C2477" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2477" t="n">
         <v>5</v>
@@ -57291,7 +57260,7 @@
         </is>
       </c>
       <c r="C2478" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2478" t="n">
         <v>16</v>
@@ -57314,7 +57283,7 @@
         </is>
       </c>
       <c r="C2479" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2479" t="n">
         <v>6</v>
@@ -57337,7 +57306,7 @@
         </is>
       </c>
       <c r="C2480" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2480" t="n">
         <v>6</v>
@@ -57360,7 +57329,7 @@
         </is>
       </c>
       <c r="C2481" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2481" t="n">
         <v>6</v>
@@ -57383,7 +57352,7 @@
         </is>
       </c>
       <c r="C2482" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2482" t="n">
         <v>6</v>
@@ -57406,7 +57375,7 @@
         </is>
       </c>
       <c r="C2483" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2483" t="n">
         <v>6</v>
@@ -57429,7 +57398,7 @@
         </is>
       </c>
       <c r="C2484" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2484" t="n">
         <v>6</v>
@@ -57452,7 +57421,7 @@
         </is>
       </c>
       <c r="C2485" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2485" t="n">
         <v>6</v>
@@ -57475,7 +57444,7 @@
         </is>
       </c>
       <c r="C2486" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2486" t="n">
         <v>30</v>
@@ -57498,7 +57467,7 @@
         </is>
       </c>
       <c r="C2487" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2487" t="n">
         <v>30</v>
@@ -57521,7 +57490,7 @@
         </is>
       </c>
       <c r="C2488" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2488" t="n">
         <v>30</v>
@@ -57544,7 +57513,7 @@
         </is>
       </c>
       <c r="C2489" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2489" t="n">
         <v>27</v>
@@ -57567,7 +57536,7 @@
         </is>
       </c>
       <c r="C2490" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2490" t="n">
         <v>12</v>
@@ -57590,7 +57559,7 @@
         </is>
       </c>
       <c r="C2491" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2491" t="n">
         <v>12</v>
@@ -57613,7 +57582,7 @@
         </is>
       </c>
       <c r="C2492" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2492" t="n">
         <v>30</v>
@@ -57636,7 +57605,7 @@
         </is>
       </c>
       <c r="C2493" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2493" t="n">
         <v>30</v>
@@ -57659,7 +57628,7 @@
         </is>
       </c>
       <c r="C2494" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2494" t="n">
         <v>30</v>
@@ -57682,7 +57651,7 @@
         </is>
       </c>
       <c r="C2495" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2495" t="n">
         <v>12</v>
@@ -57705,7 +57674,7 @@
         </is>
       </c>
       <c r="C2496" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2496" t="n">
         <v>12</v>
@@ -57728,7 +57697,7 @@
         </is>
       </c>
       <c r="C2497" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2497" t="n">
         <v>12</v>
@@ -57751,7 +57720,7 @@
         </is>
       </c>
       <c r="C2498" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2498" t="n">
         <v>12</v>
@@ -57774,7 +57743,7 @@
         </is>
       </c>
       <c r="C2499" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2499" t="n">
         <v>12</v>
@@ -57797,7 +57766,7 @@
         </is>
       </c>
       <c r="C2500" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2500" t="n">
         <v>6</v>
@@ -57820,7 +57789,7 @@
         </is>
       </c>
       <c r="C2501" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2501" t="n">
         <v>6</v>
@@ -57843,7 +57812,7 @@
         </is>
       </c>
       <c r="C2502" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2502" t="n">
         <v>12</v>
@@ -57866,7 +57835,7 @@
         </is>
       </c>
       <c r="C2503" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2503" t="n">
         <v>30</v>
@@ -57889,7 +57858,7 @@
         </is>
       </c>
       <c r="C2504" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2504" t="n">
         <v>12</v>
@@ -57912,7 +57881,7 @@
         </is>
       </c>
       <c r="C2505" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2505" t="n">
         <v>12</v>
@@ -57935,7 +57904,7 @@
         </is>
       </c>
       <c r="C2506" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2506" t="n">
         <v>24</v>
@@ -57958,7 +57927,7 @@
         </is>
       </c>
       <c r="C2507" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2507" t="n">
         <v>24</v>
@@ -57981,7 +57950,7 @@
         </is>
       </c>
       <c r="C2508" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2508" t="n">
         <v>30</v>
@@ -58004,7 +57973,7 @@
         </is>
       </c>
       <c r="C2509" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2509" t="n">
         <v>12</v>
@@ -58027,7 +57996,7 @@
         </is>
       </c>
       <c r="C2510" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2510" t="n">
         <v>12</v>
@@ -58050,7 +58019,7 @@
         </is>
       </c>
       <c r="C2511" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2511" t="n">
         <v>12</v>
@@ -58073,7 +58042,7 @@
         </is>
       </c>
       <c r="C2512" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2512" t="n">
         <v>12</v>
@@ -58096,7 +58065,7 @@
         </is>
       </c>
       <c r="C2513" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2513" t="n">
         <v>12</v>
@@ -58119,7 +58088,7 @@
         </is>
       </c>
       <c r="C2514" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2514" t="n">
         <v>12</v>
@@ -58142,7 +58111,7 @@
         </is>
       </c>
       <c r="C2515" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2515" t="n">
         <v>12</v>
@@ -58165,7 +58134,7 @@
         </is>
       </c>
       <c r="C2516" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2516" t="n">
         <v>12</v>
@@ -58188,7 +58157,7 @@
         </is>
       </c>
       <c r="C2517" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2517" t="n">
         <v>12</v>
@@ -58211,7 +58180,7 @@
         </is>
       </c>
       <c r="C2518" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D2518" t="n">
         <v>100</v>
@@ -58234,7 +58203,7 @@
         </is>
       </c>
       <c r="C2519" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2519" t="n">
         <v>12</v>
@@ -58257,7 +58226,7 @@
         </is>
       </c>
       <c r="C2520" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2520" t="n">
         <v>12</v>
@@ -58280,7 +58249,7 @@
         </is>
       </c>
       <c r="C2521" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2521" t="n">
         <v>12</v>
@@ -58303,7 +58272,7 @@
         </is>
       </c>
       <c r="C2522" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2522" t="n">
         <v>12</v>
@@ -58326,7 +58295,7 @@
         </is>
       </c>
       <c r="C2523" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2523" t="n">
         <v>12</v>
@@ -58349,7 +58318,7 @@
         </is>
       </c>
       <c r="C2524" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2524" t="n">
         <v>12</v>
@@ -58372,7 +58341,7 @@
         </is>
       </c>
       <c r="C2525" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2525" t="n">
         <v>12</v>
@@ -58395,7 +58364,7 @@
         </is>
       </c>
       <c r="C2526" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2526" t="n">
         <v>8</v>
@@ -58418,7 +58387,7 @@
         </is>
       </c>
       <c r="C2527" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2527" t="n">
         <v>12</v>
@@ -58441,7 +58410,7 @@
         </is>
       </c>
       <c r="C2528" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2528" t="n">
         <v>12</v>
@@ -58464,7 +58433,7 @@
         </is>
       </c>
       <c r="C2529" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2529" t="n">
         <v>12</v>
@@ -58487,7 +58456,7 @@
         </is>
       </c>
       <c r="C2530" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2530" t="n">
         <v>12</v>
@@ -58510,7 +58479,7 @@
         </is>
       </c>
       <c r="C2531" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2531" t="n">
         <v>12</v>
@@ -58533,7 +58502,7 @@
         </is>
       </c>
       <c r="C2532" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2532" t="n">
         <v>12</v>
@@ -58556,7 +58525,7 @@
         </is>
       </c>
       <c r="C2533" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2533" t="n">
         <v>12</v>
@@ -58579,7 +58548,7 @@
         </is>
       </c>
       <c r="C2534" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2534" t="n">
         <v>12</v>
@@ -58602,7 +58571,7 @@
         </is>
       </c>
       <c r="C2535" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2535" t="n">
         <v>12</v>
@@ -58625,7 +58594,7 @@
         </is>
       </c>
       <c r="C2536" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2536" t="n">
         <v>12</v>
@@ -58648,7 +58617,7 @@
         </is>
       </c>
       <c r="C2537" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2537" t="n">
         <v>12</v>
@@ -58671,7 +58640,7 @@
         </is>
       </c>
       <c r="C2538" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2538" t="n">
         <v>12</v>
@@ -58694,7 +58663,7 @@
         </is>
       </c>
       <c r="C2539" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2539" t="n">
         <v>12</v>
@@ -58717,7 +58686,7 @@
         </is>
       </c>
       <c r="C2540" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2540" t="n">
         <v>12</v>
@@ -58740,7 +58709,7 @@
         </is>
       </c>
       <c r="C2541" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2541" t="n">
         <v>12</v>
@@ -58763,7 +58732,7 @@
         </is>
       </c>
       <c r="C2542" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2542" t="n">
         <v>12</v>
@@ -58786,7 +58755,7 @@
         </is>
       </c>
       <c r="C2543" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2543" t="n">
         <v>12</v>
@@ -58809,7 +58778,7 @@
         </is>
       </c>
       <c r="C2544" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2544" t="n">
         <v>12</v>
@@ -58832,7 +58801,7 @@
         </is>
       </c>
       <c r="C2545" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2545" t="n">
         <v>12</v>
@@ -58855,7 +58824,7 @@
         </is>
       </c>
       <c r="C2546" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2546" t="n">
         <v>12</v>
@@ -58878,7 +58847,7 @@
         </is>
       </c>
       <c r="C2547" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2547" t="n">
         <v>12</v>
@@ -58901,7 +58870,7 @@
         </is>
       </c>
       <c r="C2548" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2548" t="n">
         <v>12</v>
@@ -58924,7 +58893,7 @@
         </is>
       </c>
       <c r="C2549" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2549" t="n">
         <v>30</v>
@@ -58947,7 +58916,7 @@
         </is>
       </c>
       <c r="C2550" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2550" t="n">
         <v>30</v>
@@ -58970,7 +58939,7 @@
         </is>
       </c>
       <c r="C2551" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2551" t="n">
         <v>30</v>
@@ -58993,7 +58962,7 @@
         </is>
       </c>
       <c r="C2552" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2552" t="n">
         <v>30</v>
@@ -59016,7 +58985,7 @@
         </is>
       </c>
       <c r="C2553" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2553" t="n">
         <v>30</v>
@@ -59039,7 +59008,7 @@
         </is>
       </c>
       <c r="C2554" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2554" t="n">
         <v>24</v>
@@ -59062,7 +59031,7 @@
         </is>
       </c>
       <c r="C2555" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2555" t="n">
         <v>30</v>
@@ -59085,7 +59054,7 @@
         </is>
       </c>
       <c r="C2556" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2556" t="n">
         <v>24</v>
@@ -59108,7 +59077,7 @@
         </is>
       </c>
       <c r="C2557" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2557" t="n">
         <v>24</v>
@@ -59131,7 +59100,7 @@
         </is>
       </c>
       <c r="C2558" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2558" t="n">
         <v>30</v>
@@ -59154,7 +59123,7 @@
         </is>
       </c>
       <c r="C2559" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2559" t="n">
         <v>24</v>
@@ -59177,7 +59146,7 @@
         </is>
       </c>
       <c r="C2560" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2560" t="n">
         <v>30</v>
@@ -59200,7 +59169,7 @@
         </is>
       </c>
       <c r="C2561" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2561" t="n">
         <v>24</v>
@@ -59223,7 +59192,7 @@
         </is>
       </c>
       <c r="C2562" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2562" t="n">
         <v>24</v>
@@ -59246,7 +59215,7 @@
         </is>
       </c>
       <c r="C2563" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2563" t="n">
         <v>30</v>
@@ -59269,7 +59238,7 @@
         </is>
       </c>
       <c r="C2564" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2564" t="n">
         <v>30</v>
@@ -59292,7 +59261,7 @@
         </is>
       </c>
       <c r="C2565" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2565" t="n">
         <v>24</v>
@@ -59315,7 +59284,7 @@
         </is>
       </c>
       <c r="C2566" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2566" t="n">
         <v>30</v>
@@ -59338,7 +59307,7 @@
         </is>
       </c>
       <c r="C2567" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2567" t="n">
         <v>30</v>
@@ -59361,7 +59330,7 @@
         </is>
       </c>
       <c r="C2568" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2568" t="n">
         <v>24</v>
@@ -59384,7 +59353,7 @@
         </is>
       </c>
       <c r="C2569" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2569" t="n">
         <v>30</v>
@@ -59407,7 +59376,7 @@
         </is>
       </c>
       <c r="C2570" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2570" t="n">
         <v>24</v>
@@ -59430,7 +59399,7 @@
         </is>
       </c>
       <c r="C2571" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2571" t="n">
         <v>8</v>
@@ -59453,7 +59422,7 @@
         </is>
       </c>
       <c r="C2572" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2572" t="n">
         <v>24</v>
@@ -59476,7 +59445,7 @@
         </is>
       </c>
       <c r="C2573" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2573" t="n">
         <v>30</v>
@@ -59499,7 +59468,7 @@
         </is>
       </c>
       <c r="C2574" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2574" t="n">
         <v>36</v>
@@ -59522,7 +59491,7 @@
         </is>
       </c>
       <c r="C2575" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2575" t="n">
         <v>16</v>
@@ -59545,7 +59514,7 @@
         </is>
       </c>
       <c r="C2576" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2576" t="n">
         <v>24</v>
@@ -59568,7 +59537,7 @@
         </is>
       </c>
       <c r="C2577" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2577" t="n">
         <v>30</v>
@@ -59591,7 +59560,7 @@
         </is>
       </c>
       <c r="C2578" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2578" t="n">
         <v>30</v>
@@ -59614,7 +59583,7 @@
         </is>
       </c>
       <c r="C2579" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2579" t="n">
         <v>20</v>
@@ -59637,7 +59606,7 @@
         </is>
       </c>
       <c r="C2580" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2580" t="n">
         <v>24</v>
@@ -59660,7 +59629,7 @@
         </is>
       </c>
       <c r="C2581" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2581" t="n">
         <v>8</v>
@@ -59683,7 +59652,7 @@
         </is>
       </c>
       <c r="C2582" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2582" t="n">
         <v>24</v>
@@ -59706,7 +59675,7 @@
         </is>
       </c>
       <c r="C2583" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2583" t="n">
         <v>24</v>
@@ -59729,7 +59698,7 @@
         </is>
       </c>
       <c r="C2584" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2584" t="n">
         <v>25</v>
@@ -59752,7 +59721,7 @@
         </is>
       </c>
       <c r="C2585" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2585" t="n">
         <v>30</v>
@@ -59775,7 +59744,7 @@
         </is>
       </c>
       <c r="C2586" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2586" t="n">
         <v>30</v>
@@ -59798,7 +59767,7 @@
         </is>
       </c>
       <c r="C2587" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2587" t="n">
         <v>30</v>
@@ -59821,7 +59790,7 @@
         </is>
       </c>
       <c r="C2588" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2588" t="n">
         <v>24</v>
@@ -59844,7 +59813,7 @@
         </is>
       </c>
       <c r="C2589" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2589" t="n">
         <v>30</v>
@@ -59867,7 +59836,7 @@
         </is>
       </c>
       <c r="C2590" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2590" t="n">
         <v>30</v>
@@ -59890,7 +59859,7 @@
         </is>
       </c>
       <c r="C2591" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2591" t="n">
         <v>30</v>
@@ -59913,7 +59882,7 @@
         </is>
       </c>
       <c r="C2592" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2592" t="n">
         <v>30</v>
@@ -59936,7 +59905,7 @@
         </is>
       </c>
       <c r="C2593" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2593" t="n">
         <v>24</v>
@@ -59959,7 +59928,7 @@
         </is>
       </c>
       <c r="C2594" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2594" t="n">
         <v>24</v>
@@ -59982,7 +59951,7 @@
         </is>
       </c>
       <c r="C2595" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2595" t="n">
         <v>24</v>
@@ -60005,7 +59974,7 @@
         </is>
       </c>
       <c r="C2596" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2596" t="n">
         <v>24</v>
@@ -60028,7 +59997,7 @@
         </is>
       </c>
       <c r="C2597" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2597" t="n">
         <v>30</v>
@@ -60051,7 +60020,7 @@
         </is>
       </c>
       <c r="C2598" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2598" t="n">
         <v>30</v>
@@ -60074,7 +60043,7 @@
         </is>
       </c>
       <c r="C2599" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2599" t="n">
         <v>12</v>
@@ -60097,7 +60066,7 @@
         </is>
       </c>
       <c r="C2600" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2600" t="n">
         <v>12</v>
@@ -60120,7 +60089,7 @@
         </is>
       </c>
       <c r="C2601" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2601" t="n">
         <v>12</v>
@@ -60143,7 +60112,7 @@
         </is>
       </c>
       <c r="C2602" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2602" t="n">
         <v>12</v>
@@ -60166,7 +60135,7 @@
         </is>
       </c>
       <c r="C2603" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2603" t="n">
         <v>12</v>
@@ -60189,7 +60158,7 @@
         </is>
       </c>
       <c r="C2604" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2604" t="n">
         <v>12</v>
@@ -60212,7 +60181,7 @@
         </is>
       </c>
       <c r="C2605" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2605" t="n">
         <v>12</v>
@@ -60235,7 +60204,7 @@
         </is>
       </c>
       <c r="C2606" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2606" t="n">
         <v>12</v>
@@ -60258,7 +60227,7 @@
         </is>
       </c>
       <c r="C2607" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2607" t="n">
         <v>12</v>
@@ -60281,7 +60250,7 @@
         </is>
       </c>
       <c r="C2608" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2608" t="n">
         <v>12</v>
@@ -60304,7 +60273,7 @@
         </is>
       </c>
       <c r="C2609" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2609" t="n">
         <v>30</v>
@@ -60327,7 +60296,7 @@
         </is>
       </c>
       <c r="C2610" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2610" t="n">
         <v>12</v>
@@ -60350,7 +60319,7 @@
         </is>
       </c>
       <c r="C2611" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2611" t="n">
         <v>12</v>
@@ -60373,7 +60342,7 @@
         </is>
       </c>
       <c r="C2612" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2612" t="n">
         <v>6</v>
@@ -60396,7 +60365,7 @@
         </is>
       </c>
       <c r="C2613" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2613" t="n">
         <v>12</v>
@@ -60419,7 +60388,7 @@
         </is>
       </c>
       <c r="C2614" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2614" t="n">
         <v>12</v>
@@ -60442,7 +60411,7 @@
         </is>
       </c>
       <c r="C2615" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2615" t="n">
         <v>12</v>
@@ -60465,7 +60434,7 @@
         </is>
       </c>
       <c r="C2616" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2616" t="n">
         <v>12</v>
@@ -60488,7 +60457,7 @@
         </is>
       </c>
       <c r="C2617" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2617" t="n">
         <v>12</v>
@@ -60511,7 +60480,7 @@
         </is>
       </c>
       <c r="C2618" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2618" t="n">
         <v>12</v>
@@ -60534,7 +60503,7 @@
         </is>
       </c>
       <c r="C2619" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2619" t="n">
         <v>6</v>
@@ -60557,7 +60526,7 @@
         </is>
       </c>
       <c r="C2620" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2620" t="n">
         <v>6</v>
@@ -60580,7 +60549,7 @@
         </is>
       </c>
       <c r="C2621" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2621" t="n">
         <v>12</v>
@@ -60603,7 +60572,7 @@
         </is>
       </c>
       <c r="C2622" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2622" t="n">
         <v>12</v>
@@ -60626,7 +60595,7 @@
         </is>
       </c>
       <c r="C2623" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2623" t="n">
         <v>12</v>
@@ -60649,7 +60618,7 @@
         </is>
       </c>
       <c r="C2624" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2624" t="n">
         <v>12</v>
@@ -60672,7 +60641,7 @@
         </is>
       </c>
       <c r="C2625" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2625" t="n">
         <v>12</v>
@@ -60695,7 +60664,7 @@
         </is>
       </c>
       <c r="C2626" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2626" t="n">
         <v>12</v>
@@ -60718,7 +60687,7 @@
         </is>
       </c>
       <c r="C2627" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2627" t="n">
         <v>12</v>
@@ -60741,7 +60710,7 @@
         </is>
       </c>
       <c r="C2628" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2628" t="n">
         <v>12</v>
@@ -60764,7 +60733,7 @@
         </is>
       </c>
       <c r="C2629" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2629" t="n">
         <v>16</v>
@@ -60787,7 +60756,7 @@
         </is>
       </c>
       <c r="C2630" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2630" t="n">
         <v>12</v>
@@ -60810,7 +60779,7 @@
         </is>
       </c>
       <c r="C2631" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2631" t="n">
         <v>16</v>
@@ -60833,7 +60802,7 @@
         </is>
       </c>
       <c r="C2632" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2632" t="n">
         <v>12</v>
@@ -60856,7 +60825,7 @@
         </is>
       </c>
       <c r="C2633" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2633" t="n">
         <v>16</v>
@@ -60879,7 +60848,7 @@
         </is>
       </c>
       <c r="C2634" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2634" t="n">
         <v>12</v>
@@ -60902,7 +60871,7 @@
         </is>
       </c>
       <c r="C2635" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2635" t="n">
         <v>16</v>
@@ -60925,7 +60894,7 @@
         </is>
       </c>
       <c r="C2636" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2636" t="n">
         <v>12</v>
@@ -60948,7 +60917,7 @@
         </is>
       </c>
       <c r="C2637" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2637" t="n">
         <v>12</v>
@@ -60971,7 +60940,7 @@
         </is>
       </c>
       <c r="C2638" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2638" t="n">
         <v>16</v>
@@ -60994,7 +60963,7 @@
         </is>
       </c>
       <c r="C2639" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2639" t="n">
         <v>12</v>
@@ -61017,7 +60986,7 @@
         </is>
       </c>
       <c r="C2640" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2640" t="n">
         <v>12</v>
@@ -61040,7 +61009,7 @@
         </is>
       </c>
       <c r="C2641" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2641" t="n">
         <v>12</v>
@@ -61063,7 +61032,7 @@
         </is>
       </c>
       <c r="C2642" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2642" t="n">
         <v>12</v>
@@ -61086,7 +61055,7 @@
         </is>
       </c>
       <c r="C2643" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2643" t="n">
         <v>24</v>
@@ -61109,7 +61078,7 @@
         </is>
       </c>
       <c r="C2644" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2644" t="n">
         <v>30</v>
@@ -61132,7 +61101,7 @@
         </is>
       </c>
       <c r="C2645" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2645" t="n">
         <v>30</v>
@@ -61155,7 +61124,7 @@
         </is>
       </c>
       <c r="C2646" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2646" t="n">
         <v>30</v>
@@ -61178,7 +61147,7 @@
         </is>
       </c>
       <c r="C2647" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2647" t="n">
         <v>24</v>
@@ -61201,7 +61170,7 @@
         </is>
       </c>
       <c r="C2648" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2648" t="n">
         <v>30</v>
@@ -61224,7 +61193,7 @@
         </is>
       </c>
       <c r="C2649" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2649" t="n">
         <v>30</v>
@@ -61247,7 +61216,7 @@
         </is>
       </c>
       <c r="C2650" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2650" t="n">
         <v>24</v>
@@ -61270,7 +61239,7 @@
         </is>
       </c>
       <c r="C2651" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2651" t="n">
         <v>30</v>
@@ -61293,7 +61262,7 @@
         </is>
       </c>
       <c r="C2652" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2652" t="n">
         <v>24</v>
@@ -61316,7 +61285,7 @@
         </is>
       </c>
       <c r="C2653" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2653" t="n">
         <v>30</v>
